--- a/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
+++ b/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,10 +14,11 @@
     <sheet name="Serial_Ports" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Discovery_Rules" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Device_Permissions" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Lookup_Table" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Types" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Lookup_Table" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">IP_Devices!$A$1:$AQ$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">IP_Devices!$A$2:$AQ$3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -470,6 +471,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE:
 </t>
@@ -499,8 +501,8 @@
               <xdr:to>
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>14</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -515,6 +517,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE:
 </t>
@@ -544,7 +547,7 @@
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>68</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:rowOff>7</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -559,6 +562,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE:
 </t>
@@ -588,7 +592,7 @@
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>-96</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -603,6 +607,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE:
 </t>
@@ -632,7 +637,7 @@
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>101</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:rowOff>7</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -647,6 +652,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -677,7 +683,7 @@
                 <xdr:col>6</xdr:col>
                 <xdr:colOff>14</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -692,6 +698,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -737,6 +744,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE:
 </t>
@@ -764,10 +772,10 @@
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>7</xdr:colOff>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>115</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -782,6 +790,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -811,9 +820,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>48</xdr:colOff>
+                <xdr:colOff>20</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -828,6 +837,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -859,7 +869,7 @@
                 <xdr:col>12</xdr:col>
                 <xdr:colOff>28</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
+                <xdr:rowOff>6</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -874,6 +884,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -897,7 +908,7 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>8</xdr:col>
-                <xdr:colOff>68</xdr:colOff>
+                <xdr:colOff>96</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
@@ -905,7 +916,7 @@
                 <xdr:col>11</xdr:col>
                 <xdr:colOff>91</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -920,6 +931,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -942,7 +954,7 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>48</xdr:colOff>
+                <xdr:colOff>76</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
@@ -950,7 +962,7 @@
                 <xdr:col>11</xdr:col>
                 <xdr:colOff>81</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
+                <xdr:rowOff>6</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -965,6 +977,145 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ZPE - OPTIONAL:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Works together with on-demand mode and defines if the device state should be detected based on icmp connectivity
+Default: blank
+Recommended: yes, when mode is set to on-demand</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>28</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ZPE - OPTIONAL:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">controlls the if multiple users can connect at teh same time to the device or not.
+Dafault: yes</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>34</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>14</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ZPE - OPTIONAL:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Device icon to be used in the WEBUI.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>15</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>17</xdr:col>
+                <xdr:colOff>14</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -1053,151 +1204,16 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>14</xdr:col>
-                <xdr:colOff>15</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>20</xdr:colOff>
-                <xdr:row>11</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="O1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">ZPE - OPTIONAL:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Works together with on-demand mode and defines if the device state should be detected based on icmp connectivity
-Default: blank
-Recommended: yes, when mode is set to on-demand</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>15</xdr:col>
-                <xdr:colOff>2</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="P1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">ZPE - OPTIONAL:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">controlls the if multiple users can connect at teh same time to the device or not.
-Dafault: yes</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>14</xdr:col>
-                <xdr:colOff>34</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>15</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="Q1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">ZPE - OPTIONAL:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Device icon to be used in the WEBUI.</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
                 <xdr:col>17</xdr:col>
                 <xdr:colOff>15</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>18</xdr:col>
-                <xdr:colOff>51</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:col>20</xdr:col>
+                <xdr:colOff>77</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1212,6 +1228,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -1242,7 +1259,7 @@
                 <xdr:col>21</xdr:col>
                 <xdr:colOff>75</xdr:colOff>
                 <xdr:row>6</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1257,6 +1274,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">ZPE - OPTIONAL:
 </t>
@@ -1287,7 +1305,7 @@
                 <xdr:col>21</xdr:col>
                 <xdr:colOff>95</xdr:colOff>
                 <xdr:row>8</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1302,6 +1320,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Default: %APPLIANCE_%IP_%PORT</t>
         </r>
@@ -1320,7 +1339,7 @@
                 <xdr:col>30</xdr:col>
                 <xdr:colOff>-10</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>-15</xdr:rowOff>
+                <xdr:rowOff>-20</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1588,8 +1607,64 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Rene Neumann</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ZPE:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Values yes/no
+Defines if the row will be exported from the xls file and imported to Nodegrid Appliance
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>15</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-94</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>4</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="613">
   <si>
     <t xml:space="preserve">📘 Nodegrid Template – Overview &amp; Usage Guide</t>
   </si>
@@ -2203,6 +2278,659 @@
     <t xml:space="preserve">cf_custom_field2</t>
   </si>
   <si>
+    <t xml:space="preserve">ccmd_enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccmd_custom_command_enabled1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ccmd_custom_command_label1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_enabled10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_script10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccmd_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">custom_command_label10</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">_template_nodegrid</t>
   </si>
   <si>
@@ -2215,12 +2943,12 @@
     <t xml:space="preserve">admin</t>
   </si>
   <si>
+    <t xml:space="preserve">zpe.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">disabled</t>
   </si>
   <si>
-    <t xml:space="preserve">zpe.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">appliance</t>
   </si>
   <si>
@@ -2236,6 +2964,105 @@
     <t xml:space="preserve">nodegrid.png</t>
   </si>
   <si>
+    <t xml:space="preserve">HPEILO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ilo3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPEILO3 template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hp.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customcommand1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPEILO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ilo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPEILO4 template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPEILO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ilo5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPEILO5 template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPEILO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ilo6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPEILO6 template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBMIMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBMIMM template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ibm_black.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBMIMM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBMIMM2 template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELLiDRAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idrac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELLiDRAC template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dell.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELLiDRAC9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idrac9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELLiDRAC9 template</t>
+  </si>
+  <si>
     <t xml:space="preserve">Device_on_ttyS1</t>
   </si>
   <si>
@@ -2323,6 +3150,78 @@
     <t xml:space="preserve">usbS1-dev1</t>
   </si>
   <si>
+    <t xml:space="preserve">clone_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">device_type_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh_options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">password_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">command_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">console_escape_sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oem_support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idrac6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ogin:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/admin[0-9]+→</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\x1c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/admin[0-9]+-&gt;|racadm&gt;&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ogin Name:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;[^&gt;]+&gt;hpiLO-&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\x1b(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-oMACs=+hmac-ripemd160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rname:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[a-zA-Z0-9 #]+&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\x1b.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes/No</t>
   </si>
   <si>
@@ -2518,9 +3417,6 @@
     <t xml:space="preserve">ttyS10</t>
   </si>
   <si>
-    <t xml:space="preserve">dell.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">ttyS11</t>
   </si>
   <si>
@@ -2566,13 +3462,7 @@
     <t xml:space="preserve">ttyS18</t>
   </si>
   <si>
-    <t xml:space="preserve">hp.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">ttyS19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibm_black.png</t>
   </si>
   <si>
     <t xml:space="preserve">ttyS20</t>
@@ -3184,7 +4074,7 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3277,6 +4167,19 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -3489,27 +4392,27 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3617,41 +4520,43 @@
     <tableColumn id="5" name="ansible_user"/>
     <tableColumn id="6" name="ansible_ssh_private_key_file"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="local_ip" displayName="local_ip" ref="A1:T3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:T3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="local_ip" displayName="local_ip" ref="A2:T3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:T3"/>
   <tableColumns count="20">
-    <tableColumn id="1" name="Export"/>
-    <tableColumn id="2" name="ansible_inventory_name"/>
-    <tableColumn id="3" name="name"/>
-    <tableColumn id="4" name="type"/>
-    <tableColumn id="5" name="description"/>
+    <tableColumn id="1" name="no"/>
+    <tableColumn id="2" name="localhost"/>
+    <tableColumn id="3" name="_template_nodegrid"/>
+    <tableColumn id="4" name="device_console"/>
+    <tableColumn id="5" name="template console server nodegrid"/>
     <tableColumn id="6" name="address_location"/>
     <tableColumn id="7" name="coordinates"/>
     <tableColumn id="8" name="web_url"/>
-    <tableColumn id="9" name="ip_address"/>
+    <tableColumn id="9" name="localhost2"/>
     <tableColumn id="10" name="port"/>
-    <tableColumn id="11" name="username"/>
+    <tableColumn id="11" name="admin"/>
     <tableColumn id="12" name="credential"/>
     <tableColumn id="13" name="password"/>
-    <tableColumn id="14" name="mode"/>
-    <tableColumn id="15" name="enable_device_state_detection_based_on_network_traffic"/>
-    <tableColumn id="16" name="multisession"/>
-    <tableColumn id="17" name="icon"/>
-    <tableColumn id="18" name="end_point"/>
+    <tableColumn id="14" name="yes"/>
+    <tableColumn id="15" name="yes2"/>
+    <tableColumn id="16" name="zpe.png"/>
+    <tableColumn id="17" name="disabled"/>
+    <tableColumn id="18" name="appliance"/>
     <tableColumn id="19" name="port_number"/>
     <tableColumn id="20" name="allow_ssh_protocol"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="local_serial" displayName="local_serial" ref="A1:W3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:W3"/>
-  <tableColumns count="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="local_serial" displayName="local_serial" ref="A1:V3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:V3"/>
+  <tableColumns count="22">
     <tableColumn id="1" name="Export"/>
     <tableColumn id="2" name="ansible_inventory_name"/>
     <tableColumn id="3" name="name"/>
@@ -3659,23 +4564,23 @@
     <tableColumn id="5" name="type"/>
     <tableColumn id="6" name="description"/>
     <tableColumn id="7" name="address_location"/>
-    <tableColumn id="8" name="mode"/>
-    <tableColumn id="9" name="username"/>
-    <tableColumn id="10" name="password"/>
-    <tableColumn id="11" name="baud_rate"/>
-    <tableColumn id="12" name="parity"/>
-    <tableColumn id="13" name="flow_control"/>
-    <tableColumn id="14" name="data_bits"/>
-    <tableColumn id="15" name="stop_bits"/>
-    <tableColumn id="16" name="rs-232_signal_for_device_state_detection"/>
-    <tableColumn id="17" name="enable_device_state_detection_based_in_data_flow"/>
-    <tableColumn id="18" name="data_flow_scan_interval"/>
-    <tableColumn id="19" name="enable_hostname_detection"/>
-    <tableColumn id="20" name="multisession"/>
-    <tableColumn id="21" name="read-write_multisession"/>
-    <tableColumn id="22" name="enable_serial_port_settings_via_escape_sequence"/>
-    <tableColumn id="23" name="icon"/>
+    <tableColumn id="8" name="username"/>
+    <tableColumn id="9" name="password"/>
+    <tableColumn id="10" name="baud_rate"/>
+    <tableColumn id="11" name="parity"/>
+    <tableColumn id="12" name="flow_control"/>
+    <tableColumn id="13" name="data_bits"/>
+    <tableColumn id="14" name="stop_bits"/>
+    <tableColumn id="15" name="rs-232_signal_for_device_state_detection"/>
+    <tableColumn id="16" name="enable_device_state_detection_based_in_data_flow"/>
+    <tableColumn id="17" name="data_flow_scan_interval"/>
+    <tableColumn id="18" name="enable_hostname_detection"/>
+    <tableColumn id="19" name="multisession"/>
+    <tableColumn id="20" name="read-write_multisession"/>
+    <tableColumn id="21" name="enable_serial_port_settings_via_escape_sequence"/>
+    <tableColumn id="22" name="icon"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3693,6 +4598,7 @@
     <tableColumn id="8" name="enforce_device_type"/>
     <tableColumn id="9" name="inherit_appliance_credentials"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -5946,7 +6852,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AS1048576"/>
+  <dimension ref="A1:BV1048576"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="27" width="9.83"/>
@@ -5959,13 +6865,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="27" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="27" width="27.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="27" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="27" width="27.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="27" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="27" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="27" width="11.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="11.39"/>
@@ -5994,7 +6900,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="19.59"/>
   </cols>
   <sheetData>
-    <row r="1" s="30" customFormat="true" ht="61.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="65.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="29" t="s">
         <v>25</v>
       </c>
@@ -6035,16 +6941,16 @@
         <v>60</v>
       </c>
       <c r="N1" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q1" s="29" t="s">
         <v>62</v>
-      </c>
-      <c r="O1" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="P1" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q1" s="29" t="s">
-        <v>74</v>
       </c>
       <c r="R1" s="29" t="s">
         <v>76</v>
@@ -6124,8 +7030,99 @@
       <c r="AQ1" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
+      <c r="AR1" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="AS1" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="AT1" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="AU1" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV1" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="AW1" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="AX1" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="AY1" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AZ1" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="BA1" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="BB1" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="BC1" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="BD1" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="BE1" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="BF1" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="BG1" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="BH1" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="BI1" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="BJ1" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="BK1" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="BL1" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="BM1" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="BN1" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="BO1" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="BP1" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="BQ1" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="BR1" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="BS1" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT1" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="BU1" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="BV1" s="30" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
@@ -6134,80 +7131,95 @@
       <c r="B2" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>204</v>
+      <c r="C2" s="27" t="s">
+        <v>235</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>207</v>
-      </c>
+      <c r="K2" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="M2" s="27"/>
       <c r="N2" s="27" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="O2" s="27" t="s">
         <v>29</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>29</v>
+        <v>239</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
       <c r="Z2" s="27" t="s">
         <v>69</v>
       </c>
+      <c r="AA2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>213</v>
+        <v>238</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>244</v>
       </c>
       <c r="N3" s="27" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="O3" s="27" t="s">
         <v>29</v>
       </c>
       <c r="P3" s="27" t="s">
-        <v>29</v>
+        <v>245</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>214</v>
+        <v>64</v>
       </c>
       <c r="R3" s="27" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="T3" s="27"/>
       <c r="Z3" s="27" t="s">
@@ -6215,941 +7227,4619 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T4" s="27"/>
+      <c r="A4" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T4" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AR4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="AS4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="AT4" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="AU4" s="0" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T5" s="27"/>
+      <c r="A5" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="N5" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q5" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T5" s="27" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T6" s="27"/>
+      <c r="A6" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="N6" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q6" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T6" s="27" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T7" s="27"/>
+      <c r="A7" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="N7" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q7" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T7" s="27" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T8" s="27"/>
+      <c r="A8" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="N8" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O8" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q8" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T8" s="27" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T9" s="27"/>
+      <c r="A9" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="N9" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O9" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q9" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T9" s="27" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T10" s="27"/>
+      <c r="A10" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="N10" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q10" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T10" s="27" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="T11" s="27"/>
+      <c r="A11" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L11" s="27"/>
+      <c r="N11" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q11" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="T11" s="27" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L12" s="27"/>
+      <c r="O12" s="27"/>
       <c r="T12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L13" s="27"/>
+      <c r="O13" s="27"/>
       <c r="T13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L14" s="27"/>
+      <c r="O14" s="27"/>
       <c r="T14" s="27"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L15" s="27"/>
+      <c r="O15" s="27"/>
       <c r="T15" s="27"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L16" s="27"/>
+      <c r="O16" s="27"/>
       <c r="T16" s="27"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L17" s="27"/>
+      <c r="O17" s="27"/>
       <c r="T17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L18" s="27"/>
+      <c r="O18" s="27"/>
       <c r="T18" s="27"/>
       <c r="Y18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L19" s="27"/>
+      <c r="O19" s="27"/>
       <c r="T19" s="27"/>
       <c r="Y19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L20" s="27"/>
+      <c r="O20" s="27"/>
       <c r="T20" s="27"/>
       <c r="Y20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L21" s="27"/>
+      <c r="O21" s="27"/>
       <c r="T21" s="27"/>
       <c r="Y21" s="29"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L22" s="27"/>
+      <c r="O22" s="27"/>
       <c r="T22" s="27"/>
       <c r="Y22" s="29"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L23" s="27"/>
+      <c r="O23" s="27"/>
       <c r="T23" s="27"/>
       <c r="Y23" s="29"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L24" s="27"/>
+      <c r="O24" s="27"/>
       <c r="T24" s="27"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L25" s="27"/>
+      <c r="O25" s="27"/>
       <c r="T25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L26" s="27"/>
+      <c r="O26" s="27"/>
       <c r="T26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L27" s="27"/>
+      <c r="O27" s="27"/>
       <c r="T27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L28" s="27"/>
+      <c r="O28" s="27"/>
       <c r="T28" s="27"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L29" s="27"/>
+      <c r="O29" s="27"/>
       <c r="T29" s="27"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L30" s="27"/>
+      <c r="O30" s="27"/>
       <c r="T30" s="27"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L31" s="27"/>
+      <c r="O31" s="27"/>
       <c r="T31" s="27"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L32" s="27"/>
+      <c r="O32" s="27"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L33" s="27"/>
+      <c r="O33" s="27"/>
       <c r="T33" s="27"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L34" s="27"/>
+      <c r="O34" s="27"/>
       <c r="T34" s="27"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L35" s="27"/>
+      <c r="O35" s="27"/>
       <c r="T35" s="27"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L36" s="27"/>
+      <c r="O36" s="27"/>
       <c r="T36" s="27"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L37" s="27"/>
+      <c r="O37" s="27"/>
       <c r="T37" s="27"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L38" s="27"/>
+      <c r="O38" s="27"/>
       <c r="T38" s="27"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L39" s="27"/>
+      <c r="O39" s="27"/>
       <c r="T39" s="27"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L40" s="27"/>
+      <c r="O40" s="27"/>
       <c r="T40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L41" s="27"/>
+      <c r="O41" s="27"/>
       <c r="T41" s="27"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L42" s="27"/>
+      <c r="O42" s="27"/>
       <c r="T42" s="27"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L43" s="27"/>
+      <c r="O43" s="27"/>
       <c r="T43" s="27"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L44" s="27"/>
+      <c r="O44" s="27"/>
       <c r="T44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L45" s="27"/>
+      <c r="O45" s="27"/>
       <c r="T45" s="27"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L46" s="27"/>
+      <c r="O46" s="27"/>
       <c r="T46" s="27"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L47" s="27"/>
+      <c r="O47" s="27"/>
       <c r="T47" s="27"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L48" s="27"/>
+      <c r="O48" s="27"/>
       <c r="T48" s="27"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L49" s="27"/>
+      <c r="O49" s="27"/>
       <c r="T49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L50" s="27"/>
+      <c r="O50" s="27"/>
       <c r="T50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L51" s="27"/>
+      <c r="O51" s="27"/>
       <c r="T51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L52" s="27"/>
+      <c r="O52" s="27"/>
       <c r="T52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L53" s="27"/>
+      <c r="O53" s="27"/>
       <c r="T53" s="27"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L54" s="27"/>
+      <c r="O54" s="27"/>
       <c r="T54" s="27"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L55" s="27"/>
+      <c r="O55" s="27"/>
       <c r="T55" s="27"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L56" s="27"/>
+      <c r="O56" s="27"/>
       <c r="T56" s="27"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L57" s="27"/>
+      <c r="O57" s="27"/>
       <c r="T57" s="27"/>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L58" s="27"/>
+      <c r="O58" s="27"/>
       <c r="T58" s="27"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L59" s="27"/>
+      <c r="O59" s="27"/>
       <c r="T59" s="27"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L60" s="27"/>
+      <c r="O60" s="27"/>
       <c r="T60" s="27"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L61" s="27"/>
+      <c r="O61" s="27"/>
       <c r="T61" s="27"/>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L62" s="27"/>
+      <c r="O62" s="27"/>
       <c r="T62" s="27"/>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L63" s="27"/>
+      <c r="O63" s="27"/>
       <c r="T63" s="27"/>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L64" s="27"/>
+      <c r="O64" s="27"/>
       <c r="T64" s="27"/>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L65" s="27"/>
+      <c r="O65" s="27"/>
       <c r="T65" s="27"/>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L66" s="27"/>
+      <c r="O66" s="27"/>
       <c r="T66" s="27"/>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L67" s="27"/>
+      <c r="O67" s="27"/>
       <c r="T67" s="27"/>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L68" s="27"/>
+      <c r="O68" s="27"/>
       <c r="T68" s="27"/>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L69" s="27"/>
+      <c r="O69" s="27"/>
       <c r="T69" s="27"/>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L70" s="27"/>
+      <c r="O70" s="27"/>
       <c r="T70" s="27"/>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L71" s="27"/>
+      <c r="O71" s="27"/>
       <c r="T71" s="27"/>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L72" s="27"/>
+      <c r="O72" s="27"/>
       <c r="T72" s="27"/>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L73" s="27"/>
+      <c r="O73" s="27"/>
       <c r="T73" s="27"/>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L74" s="27"/>
+      <c r="O74" s="27"/>
       <c r="T74" s="27"/>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L75" s="27"/>
+      <c r="O75" s="27"/>
       <c r="T75" s="27"/>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L76" s="27"/>
+      <c r="O76" s="27"/>
       <c r="T76" s="27"/>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L77" s="27"/>
+      <c r="O77" s="27"/>
       <c r="T77" s="27"/>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L78" s="27"/>
+      <c r="O78" s="27"/>
       <c r="T78" s="27"/>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L79" s="27"/>
+      <c r="O79" s="27"/>
       <c r="T79" s="27"/>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L80" s="27"/>
+      <c r="O80" s="27"/>
       <c r="T80" s="27"/>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L81" s="27"/>
+      <c r="O81" s="27"/>
       <c r="T81" s="27"/>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L82" s="27"/>
+      <c r="O82" s="27"/>
       <c r="T82" s="27"/>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L83" s="27"/>
+      <c r="O83" s="27"/>
       <c r="T83" s="27"/>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L84" s="27"/>
+      <c r="O84" s="27"/>
       <c r="T84" s="27"/>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L85" s="27"/>
+      <c r="O85" s="27"/>
       <c r="T85" s="27"/>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L86" s="27"/>
+      <c r="O86" s="27"/>
       <c r="T86" s="27"/>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L87" s="27"/>
+      <c r="O87" s="27"/>
       <c r="T87" s="27"/>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L88" s="27"/>
+      <c r="O88" s="27"/>
       <c r="T88" s="27"/>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L89" s="27"/>
+      <c r="O89" s="27"/>
       <c r="T89" s="27"/>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L90" s="27"/>
+      <c r="O90" s="27"/>
       <c r="T90" s="27"/>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L91" s="27"/>
+      <c r="O91" s="27"/>
       <c r="T91" s="27"/>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L92" s="27"/>
+      <c r="O92" s="27"/>
       <c r="T92" s="27"/>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L93" s="27"/>
+      <c r="O93" s="27"/>
       <c r="T93" s="27"/>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L94" s="27"/>
+      <c r="O94" s="27"/>
       <c r="T94" s="27"/>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L95" s="27"/>
+      <c r="O95" s="27"/>
       <c r="T95" s="27"/>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L96" s="27"/>
+      <c r="O96" s="27"/>
       <c r="T96" s="27"/>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L97" s="27"/>
+      <c r="O97" s="27"/>
       <c r="T97" s="27"/>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L98" s="27"/>
+      <c r="O98" s="27"/>
       <c r="T98" s="27"/>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L99" s="27"/>
+      <c r="O99" s="27"/>
       <c r="T99" s="27"/>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L100" s="27"/>
+      <c r="O100" s="27"/>
       <c r="T100" s="27"/>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L101" s="27"/>
+      <c r="O101" s="27"/>
       <c r="T101" s="27"/>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L102" s="27"/>
+      <c r="O102" s="27"/>
       <c r="T102" s="27"/>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L103" s="27"/>
+      <c r="O103" s="27"/>
       <c r="T103" s="27"/>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L104" s="27"/>
+      <c r="O104" s="27"/>
       <c r="T104" s="27"/>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L105" s="27"/>
+      <c r="O105" s="27"/>
       <c r="T105" s="27"/>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L106" s="27"/>
+      <c r="O106" s="27"/>
       <c r="T106" s="27"/>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L107" s="27"/>
+      <c r="O107" s="27"/>
       <c r="T107" s="27"/>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L108" s="27"/>
+      <c r="O108" s="27"/>
       <c r="T108" s="27"/>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L109" s="27"/>
+      <c r="O109" s="27"/>
       <c r="T109" s="27"/>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L110" s="27"/>
+      <c r="O110" s="27"/>
       <c r="T110" s="27"/>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L111" s="27"/>
+      <c r="O111" s="27"/>
       <c r="T111" s="27"/>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L112" s="27"/>
+      <c r="O112" s="27"/>
       <c r="T112" s="27"/>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L113" s="27"/>
+      <c r="O113" s="27"/>
       <c r="T113" s="27"/>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L114" s="27"/>
+      <c r="O114" s="27"/>
       <c r="T114" s="27"/>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L115" s="27"/>
+      <c r="O115" s="27"/>
       <c r="T115" s="27"/>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L116" s="27"/>
+      <c r="O116" s="27"/>
       <c r="T116" s="27"/>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L117" s="27"/>
+      <c r="O117" s="27"/>
       <c r="T117" s="27"/>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L118" s="27"/>
+      <c r="O118" s="27"/>
       <c r="T118" s="27"/>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L119" s="27"/>
+      <c r="O119" s="27"/>
       <c r="T119" s="27"/>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L120" s="27"/>
+      <c r="O120" s="27"/>
       <c r="T120" s="27"/>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L121" s="27"/>
+      <c r="O121" s="27"/>
       <c r="T121" s="27"/>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L122" s="27"/>
+      <c r="O122" s="27"/>
       <c r="T122" s="27"/>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L123" s="27"/>
+      <c r="O123" s="27"/>
       <c r="T123" s="27"/>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L124" s="27"/>
+      <c r="O124" s="27"/>
       <c r="T124" s="27"/>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L125" s="27"/>
+      <c r="O125" s="27"/>
       <c r="T125" s="27"/>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L126" s="27"/>
+      <c r="O126" s="27"/>
       <c r="T126" s="27"/>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L127" s="27"/>
+      <c r="O127" s="27"/>
       <c r="T127" s="27"/>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L128" s="27"/>
+      <c r="O128" s="27"/>
       <c r="T128" s="27"/>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L129" s="27"/>
+      <c r="O129" s="27"/>
       <c r="T129" s="27"/>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L130" s="27"/>
+      <c r="O130" s="27"/>
       <c r="T130" s="27"/>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L131" s="27"/>
+      <c r="O131" s="27"/>
       <c r="T131" s="27"/>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L132" s="27"/>
+      <c r="O132" s="27"/>
       <c r="T132" s="27"/>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L133" s="27"/>
+      <c r="O133" s="27"/>
       <c r="T133" s="27"/>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L134" s="27"/>
+      <c r="O134" s="27"/>
       <c r="T134" s="27"/>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L135" s="27"/>
+      <c r="O135" s="27"/>
       <c r="T135" s="27"/>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L136" s="27"/>
+      <c r="O136" s="27"/>
       <c r="T136" s="27"/>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L137" s="27"/>
+      <c r="O137" s="27"/>
       <c r="T137" s="27"/>
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L138" s="27"/>
+      <c r="O138" s="27"/>
       <c r="T138" s="27"/>
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L139" s="27"/>
+      <c r="O139" s="27"/>
       <c r="T139" s="27"/>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L140" s="27"/>
+      <c r="O140" s="27"/>
       <c r="T140" s="27"/>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L141" s="27"/>
+      <c r="O141" s="27"/>
       <c r="T141" s="27"/>
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L142" s="27"/>
+      <c r="O142" s="27"/>
       <c r="T142" s="27"/>
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L143" s="27"/>
+      <c r="O143" s="27"/>
       <c r="T143" s="27"/>
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L144" s="27"/>
+      <c r="O144" s="27"/>
       <c r="T144" s="27"/>
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L145" s="27"/>
+      <c r="O145" s="27"/>
       <c r="T145" s="27"/>
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L146" s="27"/>
+      <c r="O146" s="27"/>
       <c r="T146" s="27"/>
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L147" s="27"/>
+      <c r="O147" s="27"/>
       <c r="T147" s="27"/>
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L148" s="27"/>
+      <c r="O148" s="27"/>
       <c r="T148" s="27"/>
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L149" s="27"/>
+      <c r="O149" s="27"/>
       <c r="T149" s="27"/>
     </row>
     <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L150" s="27"/>
+      <c r="O150" s="27"/>
       <c r="T150" s="27"/>
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L151" s="27"/>
+      <c r="O151" s="27"/>
       <c r="T151" s="27"/>
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L152" s="27"/>
+      <c r="O152" s="27"/>
       <c r="T152" s="27"/>
     </row>
     <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L153" s="27"/>
+      <c r="O153" s="27"/>
       <c r="T153" s="27"/>
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L154" s="27"/>
+      <c r="O154" s="27"/>
       <c r="T154" s="27"/>
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L155" s="27"/>
+      <c r="O155" s="27"/>
       <c r="T155" s="27"/>
     </row>
     <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L156" s="27"/>
+      <c r="O156" s="27"/>
       <c r="T156" s="27"/>
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L157" s="27"/>
+      <c r="O157" s="27"/>
       <c r="T157" s="27"/>
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L158" s="27"/>
+      <c r="O158" s="27"/>
       <c r="T158" s="27"/>
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L159" s="27"/>
+      <c r="O159" s="27"/>
       <c r="T159" s="27"/>
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L160" s="27"/>
+      <c r="O160" s="27"/>
       <c r="T160" s="27"/>
     </row>
     <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L161" s="27"/>
+      <c r="O161" s="27"/>
       <c r="T161" s="27"/>
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L162" s="27"/>
+      <c r="O162" s="27"/>
       <c r="T162" s="27"/>
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L163" s="27"/>
+      <c r="O163" s="27"/>
       <c r="T163" s="27"/>
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L164" s="27"/>
+      <c r="O164" s="27"/>
       <c r="T164" s="27"/>
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L165" s="27"/>
+      <c r="O165" s="27"/>
       <c r="T165" s="27"/>
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L166" s="27"/>
+      <c r="O166" s="27"/>
       <c r="T166" s="27"/>
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L167" s="27"/>
+      <c r="O167" s="27"/>
       <c r="T167" s="27"/>
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L168" s="27"/>
+      <c r="O168" s="27"/>
       <c r="T168" s="27"/>
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L169" s="27"/>
+      <c r="O169" s="27"/>
       <c r="T169" s="27"/>
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L170" s="27"/>
+      <c r="O170" s="27"/>
       <c r="T170" s="27"/>
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L171" s="27"/>
+      <c r="O171" s="27"/>
       <c r="T171" s="27"/>
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L172" s="27"/>
+      <c r="O172" s="27"/>
       <c r="T172" s="27"/>
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L173" s="27"/>
+      <c r="O173" s="27"/>
       <c r="T173" s="27"/>
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L174" s="27"/>
+      <c r="O174" s="27"/>
       <c r="T174" s="27"/>
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L175" s="27"/>
+      <c r="O175" s="27"/>
       <c r="T175" s="27"/>
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L176" s="27"/>
+      <c r="O176" s="27"/>
       <c r="T176" s="27"/>
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L177" s="27"/>
+      <c r="O177" s="27"/>
       <c r="T177" s="27"/>
     </row>
     <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L178" s="27"/>
+      <c r="O178" s="27"/>
       <c r="T178" s="27"/>
     </row>
     <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L179" s="27"/>
+      <c r="O179" s="27"/>
       <c r="T179" s="27"/>
     </row>
     <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L180" s="27"/>
+      <c r="O180" s="27"/>
       <c r="T180" s="27"/>
     </row>
     <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L181" s="27"/>
+      <c r="O181" s="27"/>
       <c r="T181" s="27"/>
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L182" s="27"/>
+      <c r="O182" s="27"/>
       <c r="T182" s="27"/>
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L183" s="27"/>
+      <c r="O183" s="27"/>
       <c r="T183" s="27"/>
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L184" s="27"/>
+      <c r="O184" s="27"/>
       <c r="T184" s="27"/>
     </row>
     <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L185" s="27"/>
+      <c r="O185" s="27"/>
       <c r="T185" s="27"/>
     </row>
     <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L186" s="27"/>
+      <c r="O186" s="27"/>
       <c r="T186" s="27"/>
     </row>
     <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L187" s="27"/>
+      <c r="O187" s="27"/>
       <c r="T187" s="27"/>
     </row>
     <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L188" s="27"/>
+      <c r="O188" s="27"/>
       <c r="T188" s="27"/>
     </row>
     <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L189" s="27"/>
+      <c r="O189" s="27"/>
       <c r="T189" s="27"/>
     </row>
     <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L190" s="27"/>
+      <c r="O190" s="27"/>
       <c r="T190" s="27"/>
     </row>
     <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L191" s="27"/>
+      <c r="O191" s="27"/>
       <c r="T191" s="27"/>
     </row>
     <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L192" s="27"/>
+      <c r="O192" s="27"/>
       <c r="T192" s="27"/>
     </row>
     <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L193" s="27"/>
+      <c r="O193" s="27"/>
       <c r="T193" s="27"/>
     </row>
     <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L194" s="27"/>
+      <c r="O194" s="27"/>
       <c r="T194" s="27"/>
     </row>
     <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L195" s="27"/>
+      <c r="O195" s="27"/>
       <c r="T195" s="27"/>
     </row>
     <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L196" s="27"/>
+      <c r="O196" s="27"/>
       <c r="T196" s="27"/>
     </row>
     <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L197" s="27"/>
+      <c r="O197" s="27"/>
       <c r="T197" s="27"/>
     </row>
     <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L198" s="27"/>
+      <c r="O198" s="27"/>
       <c r="T198" s="27"/>
     </row>
     <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L199" s="27"/>
+      <c r="O199" s="27"/>
       <c r="T199" s="27"/>
     </row>
     <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L200" s="27"/>
+      <c r="O200" s="27"/>
       <c r="T200" s="27"/>
     </row>
     <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L201" s="27"/>
+      <c r="O201" s="27"/>
       <c r="T201" s="27"/>
     </row>
     <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L202" s="27"/>
+      <c r="O202" s="27"/>
       <c r="T202" s="27"/>
     </row>
     <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L203" s="27"/>
+      <c r="O203" s="27"/>
       <c r="T203" s="27"/>
     </row>
     <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L204" s="27"/>
+      <c r="O204" s="27"/>
       <c r="T204" s="27"/>
     </row>
     <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L205" s="27"/>
+      <c r="O205" s="27"/>
       <c r="T205" s="27"/>
     </row>
     <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L206" s="27"/>
+      <c r="O206" s="27"/>
       <c r="T206" s="27"/>
     </row>
     <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L207" s="27"/>
+      <c r="O207" s="27"/>
       <c r="T207" s="27"/>
     </row>
     <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L208" s="27"/>
+      <c r="O208" s="27"/>
       <c r="T208" s="27"/>
     </row>
     <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L209" s="27"/>
+      <c r="O209" s="27"/>
       <c r="T209" s="27"/>
     </row>
     <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L210" s="27"/>
+      <c r="O210" s="27"/>
       <c r="T210" s="27"/>
     </row>
     <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L211" s="27"/>
+      <c r="O211" s="27"/>
       <c r="T211" s="27"/>
     </row>
     <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L212" s="27"/>
+      <c r="O212" s="27"/>
       <c r="T212" s="27"/>
     </row>
     <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L213" s="27"/>
+      <c r="O213" s="27"/>
       <c r="T213" s="27"/>
     </row>
     <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L214" s="27"/>
+      <c r="O214" s="27"/>
       <c r="T214" s="27"/>
     </row>
     <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L215" s="27"/>
+      <c r="O215" s="27"/>
       <c r="T215" s="27"/>
     </row>
     <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L216" s="27"/>
+      <c r="O216" s="27"/>
       <c r="T216" s="27"/>
     </row>
     <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L217" s="27"/>
+      <c r="O217" s="27"/>
       <c r="T217" s="27"/>
     </row>
     <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L218" s="27"/>
+      <c r="O218" s="27"/>
       <c r="T218" s="27"/>
     </row>
     <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L219" s="27"/>
+      <c r="O219" s="27"/>
       <c r="T219" s="27"/>
     </row>
     <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L220" s="27"/>
+      <c r="O220" s="27"/>
       <c r="T220" s="27"/>
     </row>
     <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L221" s="27"/>
+      <c r="O221" s="27"/>
       <c r="T221" s="27"/>
     </row>
     <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L222" s="27"/>
+      <c r="O222" s="27"/>
       <c r="T222" s="27"/>
     </row>
     <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L223" s="27"/>
+      <c r="O223" s="27"/>
       <c r="T223" s="27"/>
     </row>
     <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L224" s="27"/>
+      <c r="O224" s="27"/>
       <c r="T224" s="27"/>
     </row>
     <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L225" s="27"/>
+      <c r="O225" s="27"/>
       <c r="T225" s="27"/>
     </row>
     <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L226" s="27"/>
+      <c r="O226" s="27"/>
       <c r="T226" s="27"/>
     </row>
     <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L227" s="27"/>
+      <c r="O227" s="27"/>
       <c r="T227" s="27"/>
     </row>
     <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L228" s="27"/>
+      <c r="O228" s="27"/>
       <c r="T228" s="27"/>
     </row>
     <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L229" s="27"/>
+      <c r="O229" s="27"/>
       <c r="T229" s="27"/>
     </row>
     <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L230" s="27"/>
+      <c r="O230" s="27"/>
       <c r="T230" s="27"/>
     </row>
     <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L231" s="27"/>
+      <c r="O231" s="27"/>
       <c r="T231" s="27"/>
     </row>
     <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L232" s="27"/>
+      <c r="O232" s="27"/>
       <c r="T232" s="27"/>
     </row>
     <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L233" s="27"/>
+      <c r="O233" s="27"/>
       <c r="T233" s="27"/>
     </row>
     <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L234" s="27"/>
+      <c r="O234" s="27"/>
       <c r="T234" s="27"/>
     </row>
     <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L235" s="27"/>
+      <c r="O235" s="27"/>
       <c r="T235" s="27"/>
     </row>
     <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L236" s="27"/>
+      <c r="O236" s="27"/>
       <c r="T236" s="27"/>
     </row>
     <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L237" s="27"/>
+      <c r="O237" s="27"/>
       <c r="T237" s="27"/>
     </row>
     <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L238" s="27"/>
+      <c r="O238" s="27"/>
       <c r="T238" s="27"/>
     </row>
     <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L239" s="27"/>
+      <c r="O239" s="27"/>
       <c r="T239" s="27"/>
     </row>
     <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L240" s="27"/>
+      <c r="O240" s="27"/>
       <c r="T240" s="27"/>
     </row>
     <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L241" s="27"/>
+      <c r="O241" s="27"/>
       <c r="T241" s="27"/>
     </row>
     <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L242" s="27"/>
+      <c r="O242" s="27"/>
       <c r="T242" s="27"/>
     </row>
     <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L243" s="27"/>
+      <c r="O243" s="27"/>
       <c r="T243" s="27"/>
     </row>
     <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L244" s="27"/>
+      <c r="O244" s="27"/>
       <c r="T244" s="27"/>
     </row>
     <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L245" s="27"/>
+      <c r="O245" s="27"/>
       <c r="T245" s="27"/>
     </row>
     <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L246" s="27"/>
+      <c r="O246" s="27"/>
       <c r="T246" s="27"/>
     </row>
     <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L247" s="27"/>
+      <c r="O247" s="27"/>
       <c r="T247" s="27"/>
     </row>
     <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L248" s="27"/>
+      <c r="O248" s="27"/>
       <c r="T248" s="27"/>
     </row>
     <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L249" s="27"/>
+      <c r="O249" s="27"/>
       <c r="T249" s="27"/>
     </row>
     <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L250" s="27"/>
+      <c r="O250" s="27"/>
       <c r="T250" s="27"/>
     </row>
     <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L251" s="27"/>
+      <c r="O251" s="27"/>
       <c r="T251" s="27"/>
     </row>
     <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L252" s="27"/>
+      <c r="O252" s="27"/>
       <c r="T252" s="27"/>
     </row>
     <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L253" s="27"/>
+      <c r="O253" s="27"/>
       <c r="T253" s="27"/>
     </row>
     <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L254" s="27"/>
+      <c r="O254" s="27"/>
       <c r="T254" s="27"/>
     </row>
     <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L255" s="27"/>
+      <c r="O255" s="27"/>
       <c r="T255" s="27"/>
     </row>
     <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L256" s="27"/>
+      <c r="O256" s="27"/>
       <c r="T256" s="27"/>
     </row>
     <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L257" s="27"/>
+      <c r="O257" s="27"/>
       <c r="T257" s="27"/>
     </row>
     <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L258" s="27"/>
+      <c r="O258" s="27"/>
       <c r="T258" s="27"/>
     </row>
     <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L259" s="27"/>
+      <c r="O259" s="27"/>
       <c r="T259" s="27"/>
     </row>
     <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L260" s="27"/>
+      <c r="O260" s="27"/>
       <c r="T260" s="27"/>
     </row>
     <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L261" s="27"/>
+      <c r="O261" s="27"/>
       <c r="T261" s="27"/>
     </row>
     <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L262" s="27"/>
+      <c r="O262" s="27"/>
       <c r="T262" s="27"/>
     </row>
     <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L263" s="27"/>
+      <c r="O263" s="27"/>
       <c r="T263" s="27"/>
     </row>
     <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L264" s="27"/>
+      <c r="O264" s="27"/>
       <c r="T264" s="27"/>
     </row>
     <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L265" s="27"/>
+      <c r="O265" s="27"/>
       <c r="T265" s="27"/>
     </row>
     <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L266" s="27"/>
+      <c r="O266" s="27"/>
       <c r="T266" s="27"/>
     </row>
     <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L267" s="27"/>
+      <c r="O267" s="27"/>
       <c r="T267" s="27"/>
     </row>
     <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L268" s="27"/>
+      <c r="O268" s="27"/>
       <c r="T268" s="27"/>
     </row>
     <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L269" s="27"/>
+      <c r="O269" s="27"/>
       <c r="T269" s="27"/>
     </row>
     <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L270" s="27"/>
+      <c r="O270" s="27"/>
       <c r="T270" s="27"/>
     </row>
     <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L271" s="27"/>
+      <c r="O271" s="27"/>
       <c r="T271" s="27"/>
     </row>
     <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L272" s="27"/>
+      <c r="O272" s="27"/>
       <c r="T272" s="27"/>
     </row>
     <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L273" s="27"/>
+      <c r="O273" s="27"/>
       <c r="T273" s="27"/>
     </row>
     <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L274" s="27"/>
+      <c r="O274" s="27"/>
       <c r="T274" s="27"/>
     </row>
     <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L275" s="27"/>
+      <c r="O275" s="27"/>
       <c r="T275" s="27"/>
     </row>
     <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L276" s="27"/>
+      <c r="O276" s="27"/>
       <c r="T276" s="27"/>
     </row>
     <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L277" s="27"/>
+      <c r="O277" s="27"/>
       <c r="T277" s="27"/>
     </row>
     <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L278" s="27"/>
+      <c r="O278" s="27"/>
       <c r="T278" s="27"/>
     </row>
     <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L279" s="27"/>
+      <c r="O279" s="27"/>
       <c r="T279" s="27"/>
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L280" s="27"/>
+      <c r="O280" s="27"/>
       <c r="T280" s="27"/>
     </row>
     <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L281" s="27"/>
+      <c r="O281" s="27"/>
       <c r="T281" s="27"/>
     </row>
     <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L282" s="27"/>
+      <c r="O282" s="27"/>
       <c r="T282" s="27"/>
     </row>
     <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L283" s="27"/>
+      <c r="O283" s="27"/>
       <c r="T283" s="27"/>
     </row>
     <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L284" s="27"/>
+      <c r="O284" s="27"/>
       <c r="T284" s="27"/>
     </row>
     <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L285" s="27"/>
+      <c r="O285" s="27"/>
       <c r="T285" s="27"/>
     </row>
     <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L286" s="27"/>
+      <c r="O286" s="27"/>
       <c r="T286" s="27"/>
     </row>
     <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L287" s="27"/>
+      <c r="O287" s="27"/>
       <c r="T287" s="27"/>
     </row>
     <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L288" s="27"/>
+      <c r="O288" s="27"/>
       <c r="T288" s="27"/>
     </row>
     <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L289" s="27"/>
+      <c r="O289" s="27"/>
       <c r="T289" s="27"/>
     </row>
     <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L290" s="27"/>
+      <c r="O290" s="27"/>
       <c r="T290" s="27"/>
     </row>
     <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L291" s="27"/>
+      <c r="O291" s="27"/>
       <c r="T291" s="27"/>
     </row>
     <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L292" s="27"/>
+      <c r="O292" s="27"/>
       <c r="T292" s="27"/>
     </row>
     <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L293" s="27"/>
+      <c r="O293" s="27"/>
       <c r="T293" s="27"/>
     </row>
     <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L294" s="27"/>
+      <c r="O294" s="27"/>
       <c r="T294" s="27"/>
     </row>
     <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L295" s="27"/>
+      <c r="O295" s="27"/>
       <c r="T295" s="27"/>
     </row>
     <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L296" s="27"/>
+      <c r="O296" s="27"/>
       <c r="T296" s="27"/>
     </row>
     <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L297" s="27"/>
+      <c r="O297" s="27"/>
       <c r="T297" s="27"/>
     </row>
     <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L298" s="27"/>
+      <c r="O298" s="27"/>
       <c r="T298" s="27"/>
     </row>
     <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L299" s="27"/>
+      <c r="O299" s="27"/>
       <c r="T299" s="27"/>
     </row>
     <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L300" s="27"/>
+      <c r="O300" s="27"/>
       <c r="T300" s="27"/>
     </row>
     <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L301" s="27"/>
+      <c r="O301" s="27"/>
       <c r="T301" s="27"/>
     </row>
     <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L302" s="27"/>
+      <c r="O302" s="27"/>
       <c r="T302" s="27"/>
     </row>
     <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L303" s="27"/>
+      <c r="O303" s="27"/>
       <c r="T303" s="27"/>
     </row>
     <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L304" s="27"/>
+      <c r="O304" s="27"/>
       <c r="T304" s="27"/>
     </row>
     <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L305" s="27"/>
+      <c r="O305" s="27"/>
       <c r="T305" s="27"/>
     </row>
     <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L306" s="27"/>
+      <c r="O306" s="27"/>
       <c r="T306" s="27"/>
     </row>
     <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L307" s="27"/>
+      <c r="O307" s="27"/>
       <c r="T307" s="27"/>
     </row>
     <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L308" s="27"/>
+      <c r="O308" s="27"/>
       <c r="T308" s="27"/>
     </row>
     <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L309" s="27"/>
+      <c r="O309" s="27"/>
       <c r="T309" s="27"/>
     </row>
     <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L310" s="27"/>
+      <c r="O310" s="27"/>
       <c r="T310" s="27"/>
     </row>
     <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L311" s="27"/>
+      <c r="O311" s="27"/>
       <c r="T311" s="27"/>
     </row>
     <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L312" s="27"/>
+      <c r="O312" s="27"/>
       <c r="T312" s="27"/>
+    </row>
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L313" s="27"/>
+      <c r="O313" s="27"/>
+    </row>
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L314" s="27"/>
+      <c r="O314" s="27"/>
+    </row>
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L315" s="27"/>
+      <c r="O315" s="27"/>
+    </row>
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L316" s="27"/>
+      <c r="O316" s="27"/>
+    </row>
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L317" s="27"/>
+      <c r="O317" s="27"/>
+    </row>
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L318" s="27"/>
+      <c r="O318" s="27"/>
+    </row>
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L319" s="27"/>
+      <c r="O319" s="27"/>
+    </row>
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L320" s="27"/>
+      <c r="O320" s="27"/>
+    </row>
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L321" s="27"/>
+      <c r="O321" s="27"/>
+    </row>
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L322" s="27"/>
+      <c r="O322" s="27"/>
+    </row>
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L323" s="27"/>
+      <c r="O323" s="27"/>
+    </row>
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L324" s="27"/>
+      <c r="O324" s="27"/>
+    </row>
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L325" s="27"/>
+      <c r="O325" s="27"/>
+    </row>
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L326" s="27"/>
+      <c r="O326" s="27"/>
+    </row>
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L327" s="27"/>
+      <c r="O327" s="27"/>
+    </row>
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L328" s="27"/>
+      <c r="O328" s="27"/>
+    </row>
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L329" s="27"/>
+      <c r="O329" s="27"/>
+    </row>
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L330" s="27"/>
+      <c r="O330" s="27"/>
+    </row>
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L331" s="27"/>
+      <c r="O331" s="27"/>
+    </row>
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L332" s="27"/>
+      <c r="O332" s="27"/>
+    </row>
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L333" s="27"/>
+      <c r="O333" s="27"/>
+    </row>
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L334" s="27"/>
+      <c r="O334" s="27"/>
+    </row>
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L335" s="27"/>
+      <c r="O335" s="27"/>
+    </row>
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L336" s="27"/>
+      <c r="O336" s="27"/>
+    </row>
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L337" s="27"/>
+      <c r="O337" s="27"/>
+    </row>
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L338" s="27"/>
+      <c r="O338" s="27"/>
+    </row>
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L339" s="27"/>
+      <c r="O339" s="27"/>
+    </row>
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L340" s="27"/>
+      <c r="O340" s="27"/>
+    </row>
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L341" s="27"/>
+      <c r="O341" s="27"/>
+    </row>
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L342" s="27"/>
+      <c r="O342" s="27"/>
+    </row>
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L343" s="27"/>
+      <c r="O343" s="27"/>
+    </row>
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L344" s="27"/>
+      <c r="O344" s="27"/>
+    </row>
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L345" s="27"/>
+      <c r="O345" s="27"/>
+    </row>
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L346" s="27"/>
+      <c r="O346" s="27"/>
+    </row>
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L347" s="27"/>
+      <c r="O347" s="27"/>
+    </row>
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L348" s="27"/>
+      <c r="O348" s="27"/>
+    </row>
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L349" s="27"/>
+      <c r="O349" s="27"/>
+    </row>
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L350" s="27"/>
+      <c r="O350" s="27"/>
+    </row>
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L351" s="27"/>
+      <c r="O351" s="27"/>
+    </row>
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L352" s="27"/>
+      <c r="O352" s="27"/>
+    </row>
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L353" s="27"/>
+      <c r="O353" s="27"/>
+    </row>
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L354" s="27"/>
+      <c r="O354" s="27"/>
+    </row>
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L355" s="27"/>
+      <c r="O355" s="27"/>
+    </row>
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L356" s="27"/>
+      <c r="O356" s="27"/>
+    </row>
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L357" s="27"/>
+      <c r="O357" s="27"/>
+    </row>
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L358" s="27"/>
+      <c r="O358" s="27"/>
+    </row>
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L359" s="27"/>
+      <c r="O359" s="27"/>
+    </row>
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L360" s="27"/>
+      <c r="O360" s="27"/>
+    </row>
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L361" s="27"/>
+      <c r="O361" s="27"/>
+    </row>
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L362" s="27"/>
+      <c r="O362" s="27"/>
+    </row>
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L363" s="27"/>
+      <c r="O363" s="27"/>
+    </row>
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L364" s="27"/>
+      <c r="O364" s="27"/>
+    </row>
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L365" s="27"/>
+      <c r="O365" s="27"/>
+    </row>
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L366" s="27"/>
+      <c r="O366" s="27"/>
+    </row>
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L367" s="27"/>
+      <c r="O367" s="27"/>
+    </row>
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L368" s="27"/>
+      <c r="O368" s="27"/>
+    </row>
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L369" s="27"/>
+      <c r="O369" s="27"/>
+    </row>
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L370" s="27"/>
+      <c r="O370" s="27"/>
+    </row>
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L371" s="27"/>
+      <c r="O371" s="27"/>
+    </row>
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L372" s="27"/>
+      <c r="O372" s="27"/>
+    </row>
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L373" s="27"/>
+      <c r="O373" s="27"/>
+    </row>
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L374" s="27"/>
+      <c r="O374" s="27"/>
+    </row>
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L375" s="27"/>
+      <c r="O375" s="27"/>
+    </row>
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L376" s="27"/>
+      <c r="O376" s="27"/>
+    </row>
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L377" s="27"/>
+      <c r="O377" s="27"/>
+    </row>
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L378" s="27"/>
+      <c r="O378" s="27"/>
+    </row>
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L379" s="27"/>
+      <c r="O379" s="27"/>
+    </row>
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L380" s="27"/>
+      <c r="O380" s="27"/>
+    </row>
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L381" s="27"/>
+      <c r="O381" s="27"/>
+    </row>
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L382" s="27"/>
+      <c r="O382" s="27"/>
+    </row>
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L383" s="27"/>
+      <c r="O383" s="27"/>
+    </row>
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L384" s="27"/>
+      <c r="O384" s="27"/>
+    </row>
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L385" s="27"/>
+      <c r="O385" s="27"/>
+    </row>
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L386" s="27"/>
+      <c r="O386" s="27"/>
+    </row>
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L387" s="27"/>
+      <c r="O387" s="27"/>
+    </row>
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L388" s="27"/>
+      <c r="O388" s="27"/>
+    </row>
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L389" s="27"/>
+      <c r="O389" s="27"/>
+    </row>
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L390" s="27"/>
+      <c r="O390" s="27"/>
+    </row>
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L391" s="27"/>
+      <c r="O391" s="27"/>
+    </row>
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L392" s="27"/>
+      <c r="O392" s="27"/>
+    </row>
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L393" s="27"/>
+      <c r="O393" s="27"/>
+    </row>
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L394" s="27"/>
+      <c r="O394" s="27"/>
+    </row>
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L395" s="27"/>
+      <c r="O395" s="27"/>
+    </row>
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L396" s="27"/>
+      <c r="O396" s="27"/>
+    </row>
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L397" s="27"/>
+      <c r="O397" s="27"/>
+    </row>
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L398" s="27"/>
+      <c r="O398" s="27"/>
+    </row>
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L399" s="27"/>
+      <c r="O399" s="27"/>
+    </row>
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L400" s="27"/>
+      <c r="O400" s="27"/>
+    </row>
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L401" s="27"/>
+      <c r="O401" s="27"/>
+    </row>
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L402" s="27"/>
+      <c r="O402" s="27"/>
+    </row>
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L403" s="27"/>
+      <c r="O403" s="27"/>
+    </row>
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L404" s="27"/>
+      <c r="O404" s="27"/>
+    </row>
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L405" s="27"/>
+      <c r="O405" s="27"/>
+    </row>
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L406" s="27"/>
+      <c r="O406" s="27"/>
+    </row>
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L407" s="27"/>
+      <c r="O407" s="27"/>
+    </row>
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L408" s="27"/>
+      <c r="O408" s="27"/>
+    </row>
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L409" s="27"/>
+      <c r="O409" s="27"/>
+    </row>
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L410" s="27"/>
+      <c r="O410" s="27"/>
+    </row>
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L411" s="27"/>
+      <c r="O411" s="27"/>
+    </row>
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L412" s="27"/>
+      <c r="O412" s="27"/>
+    </row>
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L413" s="27"/>
+      <c r="O413" s="27"/>
+    </row>
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L414" s="27"/>
+      <c r="O414" s="27"/>
+    </row>
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L415" s="27"/>
+      <c r="O415" s="27"/>
+    </row>
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L416" s="27"/>
+      <c r="O416" s="27"/>
+    </row>
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L417" s="27"/>
+      <c r="O417" s="27"/>
+    </row>
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L418" s="27"/>
+      <c r="O418" s="27"/>
+    </row>
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L419" s="27"/>
+      <c r="O419" s="27"/>
+    </row>
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L420" s="27"/>
+      <c r="O420" s="27"/>
+    </row>
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L421" s="27"/>
+      <c r="O421" s="27"/>
+    </row>
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L422" s="27"/>
+      <c r="O422" s="27"/>
+    </row>
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L423" s="27"/>
+      <c r="O423" s="27"/>
+    </row>
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L424" s="27"/>
+      <c r="O424" s="27"/>
+    </row>
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L425" s="27"/>
+      <c r="O425" s="27"/>
+    </row>
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L426" s="27"/>
+      <c r="O426" s="27"/>
+    </row>
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L427" s="27"/>
+      <c r="O427" s="27"/>
+    </row>
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L428" s="27"/>
+      <c r="O428" s="27"/>
+    </row>
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L429" s="27"/>
+      <c r="O429" s="27"/>
+    </row>
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L430" s="27"/>
+      <c r="O430" s="27"/>
+    </row>
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L431" s="27"/>
+      <c r="O431" s="27"/>
+    </row>
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L432" s="27"/>
+      <c r="O432" s="27"/>
+    </row>
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L433" s="27"/>
+      <c r="O433" s="27"/>
+    </row>
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L434" s="27"/>
+      <c r="O434" s="27"/>
+    </row>
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L435" s="27"/>
+      <c r="O435" s="27"/>
+    </row>
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L436" s="27"/>
+      <c r="O436" s="27"/>
+    </row>
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L437" s="27"/>
+      <c r="O437" s="27"/>
+    </row>
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L438" s="27"/>
+      <c r="O438" s="27"/>
+    </row>
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L439" s="27"/>
+      <c r="O439" s="27"/>
+    </row>
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L440" s="27"/>
+      <c r="O440" s="27"/>
+    </row>
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L441" s="27"/>
+      <c r="O441" s="27"/>
+    </row>
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L442" s="27"/>
+      <c r="O442" s="27"/>
+    </row>
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L443" s="27"/>
+      <c r="O443" s="27"/>
+    </row>
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L444" s="27"/>
+      <c r="O444" s="27"/>
+    </row>
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L445" s="27"/>
+      <c r="O445" s="27"/>
+    </row>
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L446" s="27"/>
+      <c r="O446" s="27"/>
+    </row>
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L447" s="27"/>
+      <c r="O447" s="27"/>
+    </row>
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L448" s="27"/>
+      <c r="O448" s="27"/>
+    </row>
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L449" s="27"/>
+      <c r="O449" s="27"/>
+    </row>
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L450" s="27"/>
+      <c r="O450" s="27"/>
+    </row>
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L451" s="27"/>
+      <c r="O451" s="27"/>
+    </row>
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L452" s="27"/>
+      <c r="O452" s="27"/>
+    </row>
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L453" s="27"/>
+      <c r="O453" s="27"/>
+    </row>
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L454" s="27"/>
+      <c r="O454" s="27"/>
+    </row>
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L455" s="27"/>
+      <c r="O455" s="27"/>
+    </row>
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L456" s="27"/>
+      <c r="O456" s="27"/>
+    </row>
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L457" s="27"/>
+      <c r="O457" s="27"/>
+    </row>
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L458" s="27"/>
+      <c r="O458" s="27"/>
+    </row>
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L459" s="27"/>
+      <c r="O459" s="27"/>
+    </row>
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L460" s="27"/>
+      <c r="O460" s="27"/>
+    </row>
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L461" s="27"/>
+      <c r="O461" s="27"/>
+    </row>
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L462" s="27"/>
+      <c r="O462" s="27"/>
+    </row>
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L463" s="27"/>
+      <c r="O463" s="27"/>
+    </row>
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L464" s="27"/>
+      <c r="O464" s="27"/>
+    </row>
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L465" s="27"/>
+      <c r="O465" s="27"/>
+    </row>
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L466" s="27"/>
+      <c r="O466" s="27"/>
+    </row>
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L467" s="27"/>
+      <c r="O467" s="27"/>
+    </row>
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L468" s="27"/>
+      <c r="O468" s="27"/>
+    </row>
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L469" s="27"/>
+      <c r="O469" s="27"/>
+    </row>
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L470" s="27"/>
+      <c r="O470" s="27"/>
+    </row>
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L471" s="27"/>
+      <c r="O471" s="27"/>
+    </row>
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L472" s="27"/>
+      <c r="O472" s="27"/>
+    </row>
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L473" s="27"/>
+      <c r="O473" s="27"/>
+    </row>
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L474" s="27"/>
+      <c r="O474" s="27"/>
+    </row>
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L475" s="27"/>
+      <c r="O475" s="27"/>
+    </row>
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L476" s="27"/>
+      <c r="O476" s="27"/>
+    </row>
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L477" s="27"/>
+      <c r="O477" s="27"/>
+    </row>
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L478" s="27"/>
+      <c r="O478" s="27"/>
+    </row>
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L479" s="27"/>
+      <c r="O479" s="27"/>
+    </row>
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L480" s="27"/>
+      <c r="O480" s="27"/>
+    </row>
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L481" s="27"/>
+      <c r="O481" s="27"/>
+    </row>
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L482" s="27"/>
+      <c r="O482" s="27"/>
+    </row>
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L483" s="27"/>
+      <c r="O483" s="27"/>
+    </row>
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L484" s="27"/>
+      <c r="O484" s="27"/>
+    </row>
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L485" s="27"/>
+      <c r="O485" s="27"/>
+    </row>
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L486" s="27"/>
+      <c r="O486" s="27"/>
+    </row>
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L487" s="27"/>
+      <c r="O487" s="27"/>
+    </row>
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L488" s="27"/>
+      <c r="O488" s="27"/>
+    </row>
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L489" s="27"/>
+      <c r="O489" s="27"/>
+    </row>
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L490" s="27"/>
+      <c r="O490" s="27"/>
+    </row>
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L491" s="27"/>
+      <c r="O491" s="27"/>
+    </row>
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L492" s="27"/>
+      <c r="O492" s="27"/>
+    </row>
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L493" s="27"/>
+      <c r="O493" s="27"/>
+    </row>
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L494" s="27"/>
+      <c r="O494" s="27"/>
+    </row>
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L495" s="27"/>
+      <c r="O495" s="27"/>
+    </row>
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L496" s="27"/>
+      <c r="O496" s="27"/>
+    </row>
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L497" s="27"/>
+      <c r="O497" s="27"/>
+    </row>
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L498" s="27"/>
+      <c r="O498" s="27"/>
+    </row>
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L499" s="27"/>
+      <c r="O499" s="27"/>
+    </row>
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L500" s="27"/>
+      <c r="O500" s="27"/>
+    </row>
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L501" s="27"/>
+      <c r="O501" s="27"/>
+    </row>
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L502" s="27"/>
+      <c r="O502" s="27"/>
+    </row>
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L503" s="27"/>
+      <c r="O503" s="27"/>
+    </row>
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L504" s="27"/>
+      <c r="O504" s="27"/>
+    </row>
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L505" s="27"/>
+      <c r="O505" s="27"/>
+    </row>
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L506" s="27"/>
+      <c r="O506" s="27"/>
+    </row>
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L507" s="27"/>
+      <c r="O507" s="27"/>
+    </row>
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L508" s="27"/>
+      <c r="O508" s="27"/>
+    </row>
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L509" s="27"/>
+      <c r="O509" s="27"/>
+    </row>
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L510" s="27"/>
+      <c r="O510" s="27"/>
+    </row>
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L511" s="27"/>
+      <c r="O511" s="27"/>
+    </row>
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L512" s="27"/>
+      <c r="O512" s="27"/>
+    </row>
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L513" s="27"/>
+      <c r="O513" s="27"/>
+    </row>
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L514" s="27"/>
+      <c r="O514" s="27"/>
+    </row>
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L515" s="27"/>
+      <c r="O515" s="27"/>
+    </row>
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L516" s="27"/>
+      <c r="O516" s="27"/>
+    </row>
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L517" s="27"/>
+      <c r="O517" s="27"/>
+    </row>
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L518" s="27"/>
+      <c r="O518" s="27"/>
+    </row>
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L519" s="27"/>
+      <c r="O519" s="27"/>
+    </row>
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L520" s="27"/>
+      <c r="O520" s="27"/>
+    </row>
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L521" s="27"/>
+      <c r="O521" s="27"/>
+    </row>
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L522" s="27"/>
+      <c r="O522" s="27"/>
+    </row>
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L523" s="27"/>
+      <c r="O523" s="27"/>
+    </row>
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L524" s="27"/>
+      <c r="O524" s="27"/>
+    </row>
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L525" s="27"/>
+      <c r="O525" s="27"/>
+    </row>
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L526" s="27"/>
+      <c r="O526" s="27"/>
+    </row>
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L527" s="27"/>
+      <c r="O527" s="27"/>
+    </row>
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L528" s="27"/>
+      <c r="O528" s="27"/>
+    </row>
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L529" s="27"/>
+      <c r="O529" s="27"/>
+    </row>
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L530" s="27"/>
+      <c r="O530" s="27"/>
+    </row>
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L531" s="27"/>
+      <c r="O531" s="27"/>
+    </row>
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L532" s="27"/>
+      <c r="O532" s="27"/>
+    </row>
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L533" s="27"/>
+      <c r="O533" s="27"/>
+    </row>
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L534" s="27"/>
+      <c r="O534" s="27"/>
+    </row>
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L535" s="27"/>
+      <c r="O535" s="27"/>
+    </row>
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L536" s="27"/>
+      <c r="O536" s="27"/>
+    </row>
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L537" s="27"/>
+      <c r="O537" s="27"/>
+    </row>
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L538" s="27"/>
+      <c r="O538" s="27"/>
+    </row>
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L539" s="27"/>
+      <c r="O539" s="27"/>
+    </row>
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L540" s="27"/>
+      <c r="O540" s="27"/>
+    </row>
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L541" s="27"/>
+      <c r="O541" s="27"/>
+    </row>
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L542" s="27"/>
+      <c r="O542" s="27"/>
+    </row>
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L543" s="27"/>
+      <c r="O543" s="27"/>
+    </row>
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L544" s="27"/>
+      <c r="O544" s="27"/>
+    </row>
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L545" s="27"/>
+      <c r="O545" s="27"/>
+    </row>
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L546" s="27"/>
+      <c r="O546" s="27"/>
+    </row>
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L547" s="27"/>
+      <c r="O547" s="27"/>
+    </row>
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L548" s="27"/>
+      <c r="O548" s="27"/>
+    </row>
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L549" s="27"/>
+      <c r="O549" s="27"/>
+    </row>
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L550" s="27"/>
+      <c r="O550" s="27"/>
+    </row>
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L551" s="27"/>
+      <c r="O551" s="27"/>
+    </row>
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L552" s="27"/>
+      <c r="O552" s="27"/>
+    </row>
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L553" s="27"/>
+      <c r="O553" s="27"/>
+    </row>
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L554" s="27"/>
+      <c r="O554" s="27"/>
+    </row>
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L555" s="27"/>
+      <c r="O555" s="27"/>
+    </row>
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L556" s="27"/>
+      <c r="O556" s="27"/>
+    </row>
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L557" s="27"/>
+      <c r="O557" s="27"/>
+    </row>
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L558" s="27"/>
+      <c r="O558" s="27"/>
+    </row>
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L559" s="27"/>
+      <c r="O559" s="27"/>
+    </row>
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L560" s="27"/>
+      <c r="O560" s="27"/>
+    </row>
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L561" s="27"/>
+      <c r="O561" s="27"/>
+    </row>
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L562" s="27"/>
+      <c r="O562" s="27"/>
+    </row>
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L563" s="27"/>
+      <c r="O563" s="27"/>
+    </row>
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L564" s="27"/>
+      <c r="O564" s="27"/>
+    </row>
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L565" s="27"/>
+      <c r="O565" s="27"/>
+    </row>
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L566" s="27"/>
+      <c r="O566" s="27"/>
+    </row>
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L567" s="27"/>
+      <c r="O567" s="27"/>
+    </row>
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L568" s="27"/>
+      <c r="O568" s="27"/>
+    </row>
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L569" s="27"/>
+      <c r="O569" s="27"/>
+    </row>
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L570" s="27"/>
+      <c r="O570" s="27"/>
+    </row>
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L571" s="27"/>
+      <c r="O571" s="27"/>
+    </row>
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L572" s="27"/>
+      <c r="O572" s="27"/>
+    </row>
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L573" s="27"/>
+      <c r="O573" s="27"/>
+    </row>
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L574" s="27"/>
+      <c r="O574" s="27"/>
+    </row>
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L575" s="27"/>
+      <c r="O575" s="27"/>
+    </row>
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L576" s="27"/>
+      <c r="O576" s="27"/>
+    </row>
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L577" s="27"/>
+      <c r="O577" s="27"/>
+    </row>
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L578" s="27"/>
+      <c r="O578" s="27"/>
+    </row>
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L579" s="27"/>
+      <c r="O579" s="27"/>
+    </row>
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L580" s="27"/>
+      <c r="O580" s="27"/>
+    </row>
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L581" s="27"/>
+      <c r="O581" s="27"/>
+    </row>
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L582" s="27"/>
+      <c r="O582" s="27"/>
+    </row>
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L583" s="27"/>
+      <c r="O583" s="27"/>
+    </row>
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L584" s="27"/>
+      <c r="O584" s="27"/>
+    </row>
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L585" s="27"/>
+      <c r="O585" s="27"/>
+    </row>
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L586" s="27"/>
+      <c r="O586" s="27"/>
+    </row>
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L587" s="27"/>
+      <c r="O587" s="27"/>
+    </row>
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L588" s="27"/>
+      <c r="O588" s="27"/>
+    </row>
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L589" s="27"/>
+      <c r="O589" s="27"/>
+    </row>
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L590" s="27"/>
+      <c r="O590" s="27"/>
+    </row>
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L591" s="27"/>
+      <c r="O591" s="27"/>
+    </row>
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L592" s="27"/>
+      <c r="O592" s="27"/>
+    </row>
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L593" s="27"/>
+      <c r="O593" s="27"/>
+    </row>
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L594" s="27"/>
+      <c r="O594" s="27"/>
+    </row>
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L595" s="27"/>
+      <c r="O595" s="27"/>
+    </row>
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L596" s="27"/>
+      <c r="O596" s="27"/>
+    </row>
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L597" s="27"/>
+      <c r="O597" s="27"/>
+    </row>
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L598" s="27"/>
+      <c r="O598" s="27"/>
+    </row>
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L599" s="27"/>
+      <c r="O599" s="27"/>
+    </row>
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L600" s="27"/>
+      <c r="O600" s="27"/>
+    </row>
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L601" s="27"/>
+      <c r="O601" s="27"/>
+    </row>
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L602" s="27"/>
+      <c r="O602" s="27"/>
+    </row>
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L603" s="27"/>
+      <c r="O603" s="27"/>
+    </row>
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L604" s="27"/>
+      <c r="O604" s="27"/>
+    </row>
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L605" s="27"/>
+      <c r="O605" s="27"/>
+    </row>
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L606" s="27"/>
+      <c r="O606" s="27"/>
+    </row>
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L607" s="27"/>
+      <c r="O607" s="27"/>
+    </row>
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L608" s="27"/>
+      <c r="O608" s="27"/>
+    </row>
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L609" s="27"/>
+      <c r="O609" s="27"/>
+    </row>
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L610" s="27"/>
+      <c r="O610" s="27"/>
+    </row>
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L611" s="27"/>
+      <c r="O611" s="27"/>
+    </row>
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L612" s="27"/>
+      <c r="O612" s="27"/>
+    </row>
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L613" s="27"/>
+      <c r="O613" s="27"/>
+    </row>
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L614" s="27"/>
+      <c r="O614" s="27"/>
+    </row>
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L615" s="27"/>
+      <c r="O615" s="27"/>
+    </row>
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L616" s="27"/>
+      <c r="O616" s="27"/>
+    </row>
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L617" s="27"/>
+      <c r="O617" s="27"/>
+    </row>
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L618" s="27"/>
+      <c r="O618" s="27"/>
+    </row>
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L619" s="27"/>
+      <c r="O619" s="27"/>
+    </row>
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L620" s="27"/>
+      <c r="O620" s="27"/>
+    </row>
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L621" s="27"/>
+      <c r="O621" s="27"/>
+    </row>
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L622" s="27"/>
+      <c r="O622" s="27"/>
+    </row>
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L623" s="27"/>
+      <c r="O623" s="27"/>
+    </row>
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L624" s="27"/>
+      <c r="O624" s="27"/>
+    </row>
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L625" s="27"/>
+      <c r="O625" s="27"/>
+    </row>
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L626" s="27"/>
+      <c r="O626" s="27"/>
+    </row>
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L627" s="27"/>
+      <c r="O627" s="27"/>
+    </row>
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L628" s="27"/>
+      <c r="O628" s="27"/>
+    </row>
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L629" s="27"/>
+      <c r="O629" s="27"/>
+    </row>
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L630" s="27"/>
+      <c r="O630" s="27"/>
+    </row>
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L631" s="27"/>
+      <c r="O631" s="27"/>
+    </row>
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L632" s="27"/>
+      <c r="O632" s="27"/>
+    </row>
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L633" s="27"/>
+      <c r="O633" s="27"/>
+    </row>
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L634" s="27"/>
+      <c r="O634" s="27"/>
+    </row>
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L635" s="27"/>
+      <c r="O635" s="27"/>
+    </row>
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L636" s="27"/>
+      <c r="O636" s="27"/>
+    </row>
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L637" s="27"/>
+      <c r="O637" s="27"/>
+    </row>
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L638" s="27"/>
+      <c r="O638" s="27"/>
+    </row>
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L639" s="27"/>
+      <c r="O639" s="27"/>
+    </row>
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L640" s="27"/>
+      <c r="O640" s="27"/>
+    </row>
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L641" s="27"/>
+      <c r="O641" s="27"/>
+    </row>
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L642" s="27"/>
+      <c r="O642" s="27"/>
+    </row>
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L643" s="27"/>
+      <c r="O643" s="27"/>
+    </row>
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L644" s="27"/>
+      <c r="O644" s="27"/>
+    </row>
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L645" s="27"/>
+      <c r="O645" s="27"/>
+    </row>
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L646" s="27"/>
+      <c r="O646" s="27"/>
+    </row>
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L647" s="27"/>
+      <c r="O647" s="27"/>
+    </row>
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L648" s="27"/>
+      <c r="O648" s="27"/>
+    </row>
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L649" s="27"/>
+      <c r="O649" s="27"/>
+    </row>
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L650" s="27"/>
+      <c r="O650" s="27"/>
+    </row>
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L651" s="27"/>
+      <c r="O651" s="27"/>
+    </row>
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L652" s="27"/>
+      <c r="O652" s="27"/>
+    </row>
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L653" s="27"/>
+      <c r="O653" s="27"/>
+    </row>
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L654" s="27"/>
+      <c r="O654" s="27"/>
+    </row>
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L655" s="27"/>
+      <c r="O655" s="27"/>
+    </row>
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L656" s="27"/>
+      <c r="O656" s="27"/>
+    </row>
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L657" s="27"/>
+      <c r="O657" s="27"/>
+    </row>
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L658" s="27"/>
+      <c r="O658" s="27"/>
+    </row>
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L659" s="27"/>
+      <c r="O659" s="27"/>
+    </row>
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L660" s="27"/>
+      <c r="O660" s="27"/>
+    </row>
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L661" s="27"/>
+      <c r="O661" s="27"/>
+    </row>
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L662" s="27"/>
+      <c r="O662" s="27"/>
+    </row>
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L663" s="27"/>
+      <c r="O663" s="27"/>
+    </row>
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L664" s="27"/>
+      <c r="O664" s="27"/>
+    </row>
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L665" s="27"/>
+      <c r="O665" s="27"/>
+    </row>
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L666" s="27"/>
+      <c r="O666" s="27"/>
+    </row>
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L667" s="27"/>
+      <c r="O667" s="27"/>
+    </row>
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L668" s="27"/>
+      <c r="O668" s="27"/>
+    </row>
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L669" s="27"/>
+      <c r="O669" s="27"/>
+    </row>
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L670" s="27"/>
+      <c r="O670" s="27"/>
+    </row>
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L671" s="27"/>
+      <c r="O671" s="27"/>
+    </row>
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L672" s="27"/>
+      <c r="O672" s="27"/>
+    </row>
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L673" s="27"/>
+      <c r="O673" s="27"/>
+    </row>
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L674" s="27"/>
+      <c r="O674" s="27"/>
+    </row>
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L675" s="27"/>
+      <c r="O675" s="27"/>
+    </row>
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L676" s="27"/>
+      <c r="O676" s="27"/>
+    </row>
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L677" s="27"/>
+      <c r="O677" s="27"/>
+    </row>
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L678" s="27"/>
+      <c r="O678" s="27"/>
+    </row>
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L679" s="27"/>
+      <c r="O679" s="27"/>
+    </row>
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L680" s="27"/>
+      <c r="O680" s="27"/>
+    </row>
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L681" s="27"/>
+      <c r="O681" s="27"/>
+    </row>
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L682" s="27"/>
+      <c r="O682" s="27"/>
+    </row>
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L683" s="27"/>
+      <c r="O683" s="27"/>
+    </row>
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L684" s="27"/>
+      <c r="O684" s="27"/>
+    </row>
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L685" s="27"/>
+      <c r="O685" s="27"/>
+    </row>
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L686" s="27"/>
+      <c r="O686" s="27"/>
+    </row>
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L687" s="27"/>
+      <c r="O687" s="27"/>
+    </row>
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L688" s="27"/>
+      <c r="O688" s="27"/>
+    </row>
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L689" s="27"/>
+      <c r="O689" s="27"/>
+    </row>
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L690" s="27"/>
+      <c r="O690" s="27"/>
+    </row>
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L691" s="27"/>
+      <c r="O691" s="27"/>
+    </row>
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L692" s="27"/>
+      <c r="O692" s="27"/>
+    </row>
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L693" s="27"/>
+      <c r="O693" s="27"/>
+    </row>
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L694" s="27"/>
+      <c r="O694" s="27"/>
+    </row>
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L695" s="27"/>
+      <c r="O695" s="27"/>
+    </row>
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L696" s="27"/>
+      <c r="O696" s="27"/>
+    </row>
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L697" s="27"/>
+      <c r="O697" s="27"/>
+    </row>
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L698" s="27"/>
+      <c r="O698" s="27"/>
+    </row>
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L699" s="27"/>
+      <c r="O699" s="27"/>
+    </row>
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L700" s="27"/>
+      <c r="O700" s="27"/>
+    </row>
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L701" s="27"/>
+      <c r="O701" s="27"/>
+    </row>
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L702" s="27"/>
+      <c r="O702" s="27"/>
+    </row>
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L703" s="27"/>
+      <c r="O703" s="27"/>
+    </row>
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L704" s="27"/>
+      <c r="O704" s="27"/>
+    </row>
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L705" s="27"/>
+      <c r="O705" s="27"/>
+    </row>
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L706" s="27"/>
+      <c r="O706" s="27"/>
+    </row>
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L707" s="27"/>
+      <c r="O707" s="27"/>
+    </row>
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L708" s="27"/>
+      <c r="O708" s="27"/>
+    </row>
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L709" s="27"/>
+      <c r="O709" s="27"/>
+    </row>
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L710" s="27"/>
+      <c r="O710" s="27"/>
+    </row>
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L711" s="27"/>
+      <c r="O711" s="27"/>
+    </row>
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L712" s="27"/>
+      <c r="O712" s="27"/>
+    </row>
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L713" s="27"/>
+      <c r="O713" s="27"/>
+    </row>
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L714" s="27"/>
+      <c r="O714" s="27"/>
+    </row>
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L715" s="27"/>
+      <c r="O715" s="27"/>
+    </row>
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L716" s="27"/>
+      <c r="O716" s="27"/>
+    </row>
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L717" s="27"/>
+      <c r="O717" s="27"/>
+    </row>
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L718" s="27"/>
+      <c r="O718" s="27"/>
+    </row>
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L719" s="27"/>
+      <c r="O719" s="27"/>
+    </row>
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L720" s="27"/>
+      <c r="O720" s="27"/>
+    </row>
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L721" s="27"/>
+      <c r="O721" s="27"/>
+    </row>
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L722" s="27"/>
+      <c r="O722" s="27"/>
+    </row>
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L723" s="27"/>
+      <c r="O723" s="27"/>
+    </row>
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L724" s="27"/>
+      <c r="O724" s="27"/>
+    </row>
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L725" s="27"/>
+      <c r="O725" s="27"/>
+    </row>
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L726" s="27"/>
+      <c r="O726" s="27"/>
+    </row>
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L727" s="27"/>
+      <c r="O727" s="27"/>
+    </row>
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L728" s="27"/>
+      <c r="O728" s="27"/>
+    </row>
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L729" s="27"/>
+      <c r="O729" s="27"/>
+    </row>
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L730" s="27"/>
+      <c r="O730" s="27"/>
+    </row>
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L731" s="27"/>
+      <c r="O731" s="27"/>
+    </row>
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L732" s="27"/>
+      <c r="O732" s="27"/>
+    </row>
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L733" s="27"/>
+      <c r="O733" s="27"/>
+    </row>
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L734" s="27"/>
+      <c r="O734" s="27"/>
+    </row>
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L735" s="27"/>
+      <c r="O735" s="27"/>
+    </row>
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L736" s="27"/>
+      <c r="O736" s="27"/>
+    </row>
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L737" s="27"/>
+      <c r="O737" s="27"/>
+    </row>
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L738" s="27"/>
+      <c r="O738" s="27"/>
+    </row>
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L739" s="27"/>
+      <c r="O739" s="27"/>
+    </row>
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L740" s="27"/>
+      <c r="O740" s="27"/>
+    </row>
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L741" s="27"/>
+      <c r="O741" s="27"/>
+    </row>
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L742" s="27"/>
+      <c r="O742" s="27"/>
+    </row>
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L743" s="27"/>
+      <c r="O743" s="27"/>
+    </row>
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L744" s="27"/>
+      <c r="O744" s="27"/>
+    </row>
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L745" s="27"/>
+      <c r="O745" s="27"/>
+    </row>
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L746" s="27"/>
+      <c r="O746" s="27"/>
+    </row>
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L747" s="27"/>
+      <c r="O747" s="27"/>
+    </row>
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L748" s="27"/>
+      <c r="O748" s="27"/>
+    </row>
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L749" s="27"/>
+      <c r="O749" s="27"/>
+    </row>
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L750" s="27"/>
+      <c r="O750" s="27"/>
+    </row>
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L751" s="27"/>
+      <c r="O751" s="27"/>
+    </row>
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L752" s="27"/>
+      <c r="O752" s="27"/>
+    </row>
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L753" s="27"/>
+      <c r="O753" s="27"/>
+    </row>
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L754" s="27"/>
+      <c r="O754" s="27"/>
+    </row>
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L755" s="27"/>
+      <c r="O755" s="27"/>
+    </row>
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L756" s="27"/>
+      <c r="O756" s="27"/>
+    </row>
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L757" s="27"/>
+      <c r="O757" s="27"/>
+    </row>
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L758" s="27"/>
+      <c r="O758" s="27"/>
+    </row>
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L759" s="27"/>
+      <c r="O759" s="27"/>
+    </row>
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L760" s="27"/>
+      <c r="O760" s="27"/>
+    </row>
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L761" s="27"/>
+      <c r="O761" s="27"/>
+    </row>
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L762" s="27"/>
+      <c r="O762" s="27"/>
+    </row>
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L763" s="27"/>
+      <c r="O763" s="27"/>
+    </row>
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L764" s="27"/>
+      <c r="O764" s="27"/>
+    </row>
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L765" s="27"/>
+      <c r="O765" s="27"/>
+    </row>
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L766" s="27"/>
+      <c r="O766" s="27"/>
+    </row>
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L767" s="27"/>
+      <c r="O767" s="27"/>
+    </row>
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L768" s="27"/>
+      <c r="O768" s="27"/>
+    </row>
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L769" s="27"/>
+      <c r="O769" s="27"/>
+    </row>
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L770" s="27"/>
+      <c r="O770" s="27"/>
+    </row>
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L771" s="27"/>
+      <c r="O771" s="27"/>
+    </row>
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L772" s="27"/>
+      <c r="O772" s="27"/>
+    </row>
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L773" s="27"/>
+      <c r="O773" s="27"/>
+    </row>
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L774" s="27"/>
+      <c r="O774" s="27"/>
+    </row>
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L775" s="27"/>
+      <c r="O775" s="27"/>
+    </row>
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L776" s="27"/>
+      <c r="O776" s="27"/>
+    </row>
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L777" s="27"/>
+      <c r="O777" s="27"/>
+    </row>
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L778" s="27"/>
+      <c r="O778" s="27"/>
+    </row>
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L779" s="27"/>
+      <c r="O779" s="27"/>
+    </row>
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L780" s="27"/>
+      <c r="O780" s="27"/>
+    </row>
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L781" s="27"/>
+      <c r="O781" s="27"/>
+    </row>
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L782" s="27"/>
+      <c r="O782" s="27"/>
+    </row>
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L783" s="27"/>
+      <c r="O783" s="27"/>
+    </row>
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L784" s="27"/>
+      <c r="O784" s="27"/>
+    </row>
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L785" s="27"/>
+      <c r="O785" s="27"/>
+    </row>
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L786" s="27"/>
+      <c r="O786" s="27"/>
+    </row>
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L787" s="27"/>
+      <c r="O787" s="27"/>
+    </row>
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L788" s="27"/>
+      <c r="O788" s="27"/>
+    </row>
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L789" s="27"/>
+      <c r="O789" s="27"/>
+    </row>
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L790" s="27"/>
+      <c r="O790" s="27"/>
+    </row>
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L791" s="27"/>
+      <c r="O791" s="27"/>
+    </row>
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L792" s="27"/>
+      <c r="O792" s="27"/>
+    </row>
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L793" s="27"/>
+      <c r="O793" s="27"/>
+    </row>
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L794" s="27"/>
+      <c r="O794" s="27"/>
+    </row>
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L795" s="27"/>
+      <c r="O795" s="27"/>
+    </row>
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L796" s="27"/>
+      <c r="O796" s="27"/>
+    </row>
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L797" s="27"/>
+      <c r="O797" s="27"/>
+    </row>
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L798" s="27"/>
+      <c r="O798" s="27"/>
+    </row>
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L799" s="27"/>
+      <c r="O799" s="27"/>
+    </row>
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L800" s="27"/>
+      <c r="O800" s="27"/>
+    </row>
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L801" s="27"/>
+      <c r="O801" s="27"/>
+    </row>
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L802" s="27"/>
+      <c r="O802" s="27"/>
+    </row>
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L803" s="27"/>
+      <c r="O803" s="27"/>
+    </row>
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L804" s="27"/>
+      <c r="O804" s="27"/>
+    </row>
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L805" s="27"/>
+      <c r="O805" s="27"/>
+    </row>
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L806" s="27"/>
+      <c r="O806" s="27"/>
+    </row>
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L807" s="27"/>
+      <c r="O807" s="27"/>
+    </row>
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L808" s="27"/>
+      <c r="O808" s="27"/>
+    </row>
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L809" s="27"/>
+      <c r="O809" s="27"/>
+    </row>
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L810" s="27"/>
+      <c r="O810" s="27"/>
+    </row>
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L811" s="27"/>
+      <c r="O811" s="27"/>
+    </row>
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L812" s="27"/>
+      <c r="O812" s="27"/>
+    </row>
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L813" s="27"/>
+      <c r="O813" s="27"/>
+    </row>
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L814" s="27"/>
+      <c r="O814" s="27"/>
+    </row>
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L815" s="27"/>
+      <c r="O815" s="27"/>
+    </row>
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L816" s="27"/>
+      <c r="O816" s="27"/>
+    </row>
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L817" s="27"/>
+      <c r="O817" s="27"/>
+    </row>
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L818" s="27"/>
+      <c r="O818" s="27"/>
+    </row>
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L819" s="27"/>
+      <c r="O819" s="27"/>
+    </row>
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L820" s="27"/>
+      <c r="O820" s="27"/>
+    </row>
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L821" s="27"/>
+      <c r="O821" s="27"/>
+    </row>
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L822" s="27"/>
+      <c r="O822" s="27"/>
+    </row>
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L823" s="27"/>
+      <c r="O823" s="27"/>
+    </row>
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L824" s="27"/>
+      <c r="O824" s="27"/>
+    </row>
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L825" s="27"/>
+      <c r="O825" s="27"/>
+    </row>
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L826" s="27"/>
+      <c r="O826" s="27"/>
+    </row>
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L827" s="27"/>
+      <c r="O827" s="27"/>
+    </row>
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L828" s="27"/>
+      <c r="O828" s="27"/>
+    </row>
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L829" s="27"/>
+      <c r="O829" s="27"/>
+    </row>
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L830" s="27"/>
+      <c r="O830" s="27"/>
+    </row>
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L831" s="27"/>
+      <c r="O831" s="27"/>
+    </row>
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L832" s="27"/>
+      <c r="O832" s="27"/>
+    </row>
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L833" s="27"/>
+      <c r="O833" s="27"/>
+    </row>
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L834" s="27"/>
+      <c r="O834" s="27"/>
+    </row>
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L835" s="27"/>
+      <c r="O835" s="27"/>
+    </row>
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L836" s="27"/>
+      <c r="O836" s="27"/>
+    </row>
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L837" s="27"/>
+      <c r="O837" s="27"/>
+    </row>
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L838" s="27"/>
+      <c r="O838" s="27"/>
+    </row>
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L839" s="27"/>
+      <c r="O839" s="27"/>
+    </row>
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L840" s="27"/>
+      <c r="O840" s="27"/>
+    </row>
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L841" s="27"/>
+      <c r="O841" s="27"/>
+    </row>
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L842" s="27"/>
+      <c r="O842" s="27"/>
+    </row>
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L843" s="27"/>
+      <c r="O843" s="27"/>
+    </row>
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L844" s="27"/>
+      <c r="O844" s="27"/>
+    </row>
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L845" s="27"/>
+      <c r="O845" s="27"/>
+    </row>
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L846" s="27"/>
+      <c r="O846" s="27"/>
+    </row>
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L847" s="27"/>
+      <c r="O847" s="27"/>
+    </row>
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L848" s="27"/>
+      <c r="O848" s="27"/>
+    </row>
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L849" s="27"/>
+      <c r="O849" s="27"/>
+    </row>
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L850" s="27"/>
+      <c r="O850" s="27"/>
+    </row>
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L851" s="27"/>
+      <c r="O851" s="27"/>
+    </row>
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L852" s="27"/>
+      <c r="O852" s="27"/>
+    </row>
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L853" s="27"/>
+      <c r="O853" s="27"/>
+    </row>
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L854" s="27"/>
+      <c r="O854" s="27"/>
+    </row>
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L855" s="27"/>
+      <c r="O855" s="27"/>
+    </row>
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L856" s="27"/>
+      <c r="O856" s="27"/>
+    </row>
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L857" s="27"/>
+      <c r="O857" s="27"/>
+    </row>
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L858" s="27"/>
+      <c r="O858" s="27"/>
+    </row>
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L859" s="27"/>
+      <c r="O859" s="27"/>
+    </row>
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L860" s="27"/>
+      <c r="O860" s="27"/>
+    </row>
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L861" s="27"/>
+      <c r="O861" s="27"/>
+    </row>
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L862" s="27"/>
+      <c r="O862" s="27"/>
+    </row>
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L863" s="27"/>
+      <c r="O863" s="27"/>
+    </row>
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L864" s="27"/>
+      <c r="O864" s="27"/>
+    </row>
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L865" s="27"/>
+      <c r="O865" s="27"/>
+    </row>
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L866" s="27"/>
+      <c r="O866" s="27"/>
+    </row>
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L867" s="27"/>
+      <c r="O867" s="27"/>
+    </row>
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L868" s="27"/>
+      <c r="O868" s="27"/>
+    </row>
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L869" s="27"/>
+      <c r="O869" s="27"/>
+    </row>
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L870" s="27"/>
+      <c r="O870" s="27"/>
+    </row>
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L871" s="27"/>
+      <c r="O871" s="27"/>
+    </row>
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L872" s="27"/>
+      <c r="O872" s="27"/>
+    </row>
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L873" s="27"/>
+      <c r="O873" s="27"/>
+    </row>
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L874" s="27"/>
+      <c r="O874" s="27"/>
+    </row>
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L875" s="27"/>
+      <c r="O875" s="27"/>
+    </row>
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L876" s="27"/>
+      <c r="O876" s="27"/>
+    </row>
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L877" s="27"/>
+      <c r="O877" s="27"/>
+    </row>
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L878" s="27"/>
+      <c r="O878" s="27"/>
+    </row>
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L879" s="27"/>
+      <c r="O879" s="27"/>
+    </row>
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L880" s="27"/>
+      <c r="O880" s="27"/>
+    </row>
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L881" s="27"/>
+      <c r="O881" s="27"/>
+    </row>
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L882" s="27"/>
+      <c r="O882" s="27"/>
+    </row>
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L883" s="27"/>
+      <c r="O883" s="27"/>
+    </row>
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L884" s="27"/>
+      <c r="O884" s="27"/>
+    </row>
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L885" s="27"/>
+      <c r="O885" s="27"/>
+    </row>
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L886" s="27"/>
+      <c r="O886" s="27"/>
+    </row>
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L887" s="27"/>
+      <c r="O887" s="27"/>
+    </row>
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L888" s="27"/>
+      <c r="O888" s="27"/>
+    </row>
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L889" s="27"/>
+      <c r="O889" s="27"/>
+    </row>
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L890" s="27"/>
+      <c r="O890" s="27"/>
+    </row>
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L891" s="27"/>
+      <c r="O891" s="27"/>
+    </row>
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L892" s="27"/>
+      <c r="O892" s="27"/>
+    </row>
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L893" s="27"/>
+      <c r="O893" s="27"/>
+    </row>
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L894" s="27"/>
+      <c r="O894" s="27"/>
+    </row>
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L895" s="27"/>
+      <c r="O895" s="27"/>
+    </row>
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L896" s="27"/>
+      <c r="O896" s="27"/>
+    </row>
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L897" s="27"/>
+      <c r="O897" s="27"/>
+    </row>
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L898" s="27"/>
+      <c r="O898" s="27"/>
+    </row>
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L899" s="27"/>
+      <c r="O899" s="27"/>
+    </row>
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L900" s="27"/>
+      <c r="O900" s="27"/>
+    </row>
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L901" s="27"/>
+      <c r="O901" s="27"/>
+    </row>
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L902" s="27"/>
+      <c r="O902" s="27"/>
+    </row>
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L903" s="27"/>
+      <c r="O903" s="27"/>
+    </row>
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L904" s="27"/>
+      <c r="O904" s="27"/>
+    </row>
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L905" s="27"/>
+      <c r="O905" s="27"/>
+    </row>
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L906" s="27"/>
+      <c r="O906" s="27"/>
+    </row>
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L907" s="27"/>
+      <c r="O907" s="27"/>
+    </row>
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L908" s="27"/>
+      <c r="O908" s="27"/>
+    </row>
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L909" s="27"/>
+      <c r="O909" s="27"/>
+    </row>
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L910" s="27"/>
+      <c r="O910" s="27"/>
+    </row>
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L911" s="27"/>
+      <c r="O911" s="27"/>
+    </row>
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L912" s="27"/>
+      <c r="O912" s="27"/>
+    </row>
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L913" s="27"/>
+      <c r="O913" s="27"/>
+    </row>
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L914" s="27"/>
+      <c r="O914" s="27"/>
+    </row>
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L915" s="27"/>
+      <c r="O915" s="27"/>
+    </row>
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L916" s="27"/>
+      <c r="O916" s="27"/>
+    </row>
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L917" s="27"/>
+      <c r="O917" s="27"/>
+    </row>
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L918" s="27"/>
+      <c r="O918" s="27"/>
+    </row>
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L919" s="27"/>
+      <c r="O919" s="27"/>
+    </row>
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L920" s="27"/>
+      <c r="O920" s="27"/>
+    </row>
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L921" s="27"/>
+      <c r="O921" s="27"/>
+    </row>
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L922" s="27"/>
+      <c r="O922" s="27"/>
+    </row>
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L923" s="27"/>
+      <c r="O923" s="27"/>
+    </row>
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L924" s="27"/>
+      <c r="O924" s="27"/>
+    </row>
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L925" s="27"/>
+      <c r="O925" s="27"/>
+    </row>
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L926" s="27"/>
+      <c r="O926" s="27"/>
+    </row>
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L927" s="27"/>
+      <c r="O927" s="27"/>
+    </row>
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L928" s="27"/>
+      <c r="O928" s="27"/>
+    </row>
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L929" s="27"/>
+      <c r="O929" s="27"/>
+    </row>
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L930" s="27"/>
+      <c r="O930" s="27"/>
+    </row>
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L931" s="27"/>
+      <c r="O931" s="27"/>
+    </row>
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L932" s="27"/>
+      <c r="O932" s="27"/>
+    </row>
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L933" s="27"/>
+      <c r="O933" s="27"/>
+    </row>
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L934" s="27"/>
+      <c r="O934" s="27"/>
+    </row>
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L935" s="27"/>
+      <c r="O935" s="27"/>
+    </row>
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L936" s="27"/>
+      <c r="O936" s="27"/>
+    </row>
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L937" s="27"/>
+      <c r="O937" s="27"/>
+    </row>
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L938" s="27"/>
+      <c r="O938" s="27"/>
+    </row>
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L939" s="27"/>
+      <c r="O939" s="27"/>
+    </row>
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L940" s="27"/>
+      <c r="O940" s="27"/>
+    </row>
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L941" s="27"/>
+      <c r="O941" s="27"/>
+    </row>
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L942" s="27"/>
+      <c r="O942" s="27"/>
+    </row>
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L943" s="27"/>
+      <c r="O943" s="27"/>
+    </row>
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L944" s="27"/>
+      <c r="O944" s="27"/>
+    </row>
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L945" s="27"/>
+      <c r="O945" s="27"/>
+    </row>
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L946" s="27"/>
+      <c r="O946" s="27"/>
+    </row>
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L947" s="27"/>
+      <c r="O947" s="27"/>
+    </row>
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L948" s="27"/>
+      <c r="O948" s="27"/>
+    </row>
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L949" s="27"/>
+      <c r="O949" s="27"/>
+    </row>
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L950" s="27"/>
+      <c r="O950" s="27"/>
+    </row>
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L951" s="27"/>
+      <c r="O951" s="27"/>
+    </row>
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L952" s="27"/>
+      <c r="O952" s="27"/>
+    </row>
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L953" s="27"/>
+      <c r="O953" s="27"/>
+    </row>
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L954" s="27"/>
+      <c r="O954" s="27"/>
+    </row>
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L955" s="27"/>
+      <c r="O955" s="27"/>
+    </row>
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L956" s="27"/>
+      <c r="O956" s="27"/>
+    </row>
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L957" s="27"/>
+      <c r="O957" s="27"/>
+    </row>
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L958" s="27"/>
+      <c r="O958" s="27"/>
+    </row>
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L959" s="27"/>
+      <c r="O959" s="27"/>
+    </row>
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L960" s="27"/>
+      <c r="O960" s="27"/>
+    </row>
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L961" s="27"/>
+      <c r="O961" s="27"/>
+    </row>
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L962" s="27"/>
+      <c r="O962" s="27"/>
+    </row>
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L963" s="27"/>
+      <c r="O963" s="27"/>
+    </row>
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L964" s="27"/>
+      <c r="O964" s="27"/>
+    </row>
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L965" s="27"/>
+      <c r="O965" s="27"/>
+    </row>
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L966" s="27"/>
+      <c r="O966" s="27"/>
+    </row>
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L967" s="27"/>
+      <c r="O967" s="27"/>
+    </row>
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L968" s="27"/>
+      <c r="O968" s="27"/>
+    </row>
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L969" s="27"/>
+      <c r="O969" s="27"/>
+    </row>
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L970" s="27"/>
+      <c r="O970" s="27"/>
+    </row>
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L971" s="27"/>
+      <c r="O971" s="27"/>
+    </row>
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L972" s="27"/>
+      <c r="O972" s="27"/>
+    </row>
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L973" s="27"/>
+      <c r="O973" s="27"/>
+    </row>
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L974" s="27"/>
+      <c r="O974" s="27"/>
+    </row>
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L975" s="27"/>
+      <c r="O975" s="27"/>
+    </row>
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L976" s="27"/>
+      <c r="O976" s="27"/>
+    </row>
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L977" s="27"/>
+      <c r="O977" s="27"/>
+    </row>
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L978" s="27"/>
+      <c r="O978" s="27"/>
+    </row>
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L979" s="27"/>
+      <c r="O979" s="27"/>
+    </row>
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L980" s="27"/>
+      <c r="O980" s="27"/>
+    </row>
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L981" s="27"/>
+      <c r="O981" s="27"/>
+    </row>
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L982" s="27"/>
+      <c r="O982" s="27"/>
+    </row>
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L983" s="27"/>
+      <c r="O983" s="27"/>
+    </row>
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L984" s="27"/>
+      <c r="O984" s="27"/>
+    </row>
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L985" s="27"/>
+      <c r="O985" s="27"/>
+    </row>
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L986" s="27"/>
+      <c r="O986" s="27"/>
+    </row>
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L987" s="27"/>
+      <c r="O987" s="27"/>
+    </row>
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L988" s="27"/>
+      <c r="O988" s="27"/>
+    </row>
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L989" s="27"/>
+      <c r="O989" s="27"/>
+    </row>
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L990" s="27"/>
+      <c r="O990" s="27"/>
+    </row>
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L991" s="27"/>
+      <c r="O991" s="27"/>
+    </row>
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L992" s="27"/>
+      <c r="O992" s="27"/>
+    </row>
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L993" s="27"/>
+      <c r="O993" s="27"/>
+    </row>
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L994" s="27"/>
+      <c r="O994" s="27"/>
+    </row>
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L995" s="27"/>
+      <c r="O995" s="27"/>
+    </row>
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L996" s="27"/>
+      <c r="O996" s="27"/>
+    </row>
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L997" s="27"/>
+      <c r="O997" s="27"/>
+    </row>
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L998" s="27"/>
+      <c r="O998" s="27"/>
+    </row>
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L999" s="27"/>
+      <c r="O999" s="27"/>
+    </row>
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L1000" s="27"/>
+      <c r="O1000" s="27"/>
+    </row>
+    <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L1001" s="27"/>
+      <c r="O1001" s="27"/>
+    </row>
+    <row r="1002" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L1002" s="27"/>
+      <c r="O1002" s="27"/>
+    </row>
+    <row r="1003" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L1003" s="27"/>
+      <c r="O1003" s="27"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:AQ3"/>
+  <autoFilter ref="A2:AQ3"/>
   <dataValidations count="18">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J3" type="whole">
       <formula1>1</formula1>
@@ -7159,15 +11849,11 @@
       <formula1>1</formula1>
       <formula2>96</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D1003" type="list">
-      <formula1>Lookup_Table!$A$2:$A$25</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O313 T2:T312 O314:O1003" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N313 T2:T312 N314:N1003" type="list">
       <formula1>Lookup_Table!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="Q2:Q1003" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="P2:P1003" type="list">
       <formula1>Lookup_Table!$E$2:$E$202</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7175,7 +11861,7 @@
       <formula1>Lookup_Table!$J$2:$J$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N1003" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="Q2:Q1003" type="list">
       <formula1>Lookup_Table!$G$2:$G$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7191,7 +11877,7 @@
       <formula1>NGM!$B$2:$B2500</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="P2:P1003 V2:V1003 Z2:Z1003 AD2:AD1003 AF2:AF1003 AO2:AO1003" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O1003 V2:V1003 Z2:Z1003 AD2:AD1003 AF2:AF1003 AO2:AO1003" type="list">
       <formula1>Lookup_Table!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7221,6 +11907,10 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AB2:AB1003" type="list">
       <formula1>Lookup_Table!$AG$2:$AG$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D7 C8:C9 D10 C11 D12:D1011" type="none">
+      <formula1>Lookup_Table!$A$2:$A$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7253,18 +11943,19 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="11.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="37.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="26.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="23.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="45.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="37.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="23.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="45.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7290,52 +11981,52 @@
         <v>50</v>
       </c>
       <c r="H1" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="O1" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="P1" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q1" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="R1" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="S1" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="V1" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="W1" s="28" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="N1" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="O1" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="P1" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q1" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="R1" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="S1" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="T1" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="V1" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="W1" s="28" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7346,58 +12037,58 @@
         <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>215</v>
+        <v>279</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="G2" s="31"/>
+        <v>281</v>
+      </c>
+      <c r="G2" s="32"/>
       <c r="H2" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>115200</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="W2" s="33" t="s">
         <v>150</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>115200</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="27" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7408,53 +12099,53 @@
         <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>221</v>
+        <v>285</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="J3" s="1" t="n">
+        <v>9600</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="W3" s="33" t="s">
         <v>150</v>
-      </c>
-      <c r="I3" s="31"/>
-      <c r="K3" s="1" t="n">
-        <v>9600</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q3" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" s="27" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7462,7 +12153,7 @@
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A3 Q2:Q3 S2:V3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A3 P2:P3 R2:U3" type="list">
       <formula1>Lookup_Table!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7470,31 +12161,31 @@
       <formula1>Lookup_Table!$L$2:$L$301</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="W2:W3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="V2:V3" type="list">
       <formula1>Lookup_Table!$E$2:$E$149</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K2:K3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J3" type="list">
       <formula1>Lookup_Table!$N$2:$N$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2:L3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K2:K3" type="list">
       <formula1>Lookup_Table!$P$2:$P$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M2:M3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2:L3" type="list">
       <formula1>Lookup_Table!$R$2:$R$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M2:M3" type="list">
       <formula1>Lookup_Table!$T$2:$T$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N3" type="list">
       <formula1>Lookup_Table!$V$2:$V$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="P2:P3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O3" type="list">
       <formula1>Lookup_Table!$X$2:$X$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7506,7 +12197,7 @@
       <formula1>Lookup_Table!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H2:H3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="W2:W3" type="list">
       <formula1>Lookup_Table!$H$2:$H$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7572,25 +12263,25 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>223</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>159</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>29</v>
@@ -7604,22 +12295,22 @@
         <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>159</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>29</v>
@@ -7633,22 +12324,22 @@
         <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>159</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>29</v>
@@ -7760,25 +12451,25 @@
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>230</v>
+        <v>293</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>294</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>69</v>
@@ -7819,209 +12510,209 @@
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>233</v>
+        <v>293</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>297</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>237</v>
+        <v>300</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>301</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>238</v>
+        <v>293</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>302</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>233</v>
+        <v>293</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>297</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>239</v>
+        <v>293</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>303</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>230</v>
+        <v>304</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>294</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>238</v>
+        <v>304</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>302</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>243</v>
+        <v>307</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -8029,14 +12720,315 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="23.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="18.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+    </row>
+    <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="E9" s="31"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFFC000"/>
@@ -8071,28 +13063,28 @@
         <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>332</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>247</v>
+        <v>335</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>249</v>
+        <v>337</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>250</v>
+        <v>338</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>134</v>
@@ -8104,7 +13096,7 @@
         <v>138</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>252</v>
+        <v>340</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>171</v>
@@ -8142,34 +13134,34 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="T2" s="1" t="n">
         <v>5</v>
@@ -8178,51 +13170,51 @@
         <v>1</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>256</v>
+        <v>344</v>
       </c>
       <c r="AH2" s="27" t="s">
-        <v>257</v>
+        <v>345</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>258</v>
+        <v>346</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>260</v>
+        <v>348</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>261</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>263</v>
+        <v>351</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>64</v>
@@ -8231,19 +13223,19 @@
         <v>150</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>264</v>
+        <v>352</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>221</v>
+        <v>285</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>9600</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>265</v>
+        <v>353</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>266</v>
+        <v>354</v>
       </c>
       <c r="T3" s="1" t="n">
         <v>6</v>
@@ -8252,48 +13244,48 @@
         <v>2</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>267</v>
+        <v>355</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>268</v>
+        <v>356</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>271</v>
+        <v>359</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>272</v>
+        <v>360</v>
       </c>
       <c r="AH3" s="27" t="s">
-        <v>273</v>
+        <v>361</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>276</v>
+        <v>364</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>278</v>
+        <v>366</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>279</v>
+        <v>367</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>150</v>
@@ -8302,58 +13294,58 @@
         <v>64</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>280</v>
+        <v>368</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>281</v>
+        <v>369</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>19200</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>282</v>
+        <v>370</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>283</v>
+        <v>371</v>
       </c>
       <c r="T4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="AG4" s="1"/>
       <c r="AI4" s="1" t="s">
-        <v>286</v>
+        <v>374</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>287</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>288</v>
+        <v>376</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>289</v>
+        <v>377</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>290</v>
+        <v>378</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>57600</v>
@@ -8362,1084 +13354,1084 @@
         <v>8</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>291</v>
+        <v>379</v>
       </c>
       <c r="AG5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>293</v>
+        <v>381</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>294</v>
+        <v>382</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>295</v>
+        <v>383</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>38400</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="AG6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>297</v>
+        <v>385</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>298</v>
+        <v>386</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>299</v>
+        <v>387</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>115200</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>300</v>
+        <v>388</v>
       </c>
       <c r="AG7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E8" s="1" t="s">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>302</v>
+        <v>390</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>230400</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>303</v>
+        <v>391</v>
       </c>
       <c r="AG8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E9" s="1" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>304</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E10" s="1" t="s">
-        <v>305</v>
+        <v>393</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>306</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
-        <v>307</v>
+        <v>395</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>308</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>310</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E13" s="1" t="s">
-        <v>311</v>
+        <v>398</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E14" s="1" t="s">
-        <v>313</v>
+        <v>400</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>314</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E15" s="1" t="s">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>316</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E16" s="1" t="s">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>318</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="1" t="s">
-        <v>319</v>
+        <v>406</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>320</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E18" s="1" t="s">
-        <v>321</v>
+        <v>408</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>322</v>
+        <v>409</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E19" s="1" t="s">
-        <v>323</v>
+        <v>410</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>324</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="1" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>326</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="1" t="s">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>328</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E22" s="1" t="s">
-        <v>329</v>
+        <v>414</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>330</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="1" t="s">
-        <v>331</v>
+        <v>416</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>332</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="1" t="s">
-        <v>333</v>
+        <v>418</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="1" t="s">
-        <v>335</v>
+        <v>420</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>336</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="1" t="s">
-        <v>337</v>
+        <v>422</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>338</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="1" t="s">
-        <v>339</v>
+        <v>424</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>340</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E28" s="1" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>341</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E29" s="1" t="s">
-        <v>342</v>
+        <v>427</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>343</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E30" s="1" t="s">
-        <v>344</v>
+        <v>429</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>345</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="1" t="s">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>347</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="1" t="s">
-        <v>348</v>
+        <v>433</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>349</v>
+        <v>434</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E33" s="1" t="s">
-        <v>350</v>
+        <v>435</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>351</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="1" t="s">
-        <v>352</v>
+        <v>437</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>353</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="1" t="s">
-        <v>354</v>
+        <v>439</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>355</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E36" s="1" t="s">
-        <v>356</v>
+        <v>441</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>357</v>
+        <v>442</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="1" t="s">
-        <v>358</v>
+        <v>443</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>359</v>
+        <v>444</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="1" t="s">
-        <v>360</v>
+        <v>445</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>361</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="1" t="s">
-        <v>362</v>
+        <v>447</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>363</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="1" t="s">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>365</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E41" s="1" t="s">
-        <v>366</v>
+        <v>451</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>367</v>
+        <v>452</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="1" t="s">
-        <v>368</v>
+        <v>453</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>369</v>
+        <v>454</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="1" t="s">
-        <v>370</v>
+        <v>455</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>371</v>
+        <v>456</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E44" s="1" t="s">
-        <v>372</v>
+        <v>457</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>373</v>
+        <v>458</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E45" s="1" t="s">
-        <v>374</v>
+        <v>459</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>375</v>
+        <v>460</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E46" s="1" t="s">
-        <v>376</v>
+        <v>461</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>377</v>
+        <v>462</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E47" s="1" t="s">
-        <v>378</v>
+        <v>463</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>379</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E48" s="1" t="s">
-        <v>380</v>
+        <v>465</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>381</v>
+        <v>466</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E49" s="1" t="s">
-        <v>382</v>
+        <v>467</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>383</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E50" s="1" t="s">
-        <v>384</v>
+        <v>469</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>385</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E51" s="1" t="s">
-        <v>386</v>
+        <v>471</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>387</v>
+        <v>472</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E52" s="1" t="s">
-        <v>388</v>
+        <v>473</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>389</v>
+        <v>474</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E53" s="1" t="s">
-        <v>390</v>
+        <v>475</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>391</v>
+        <v>476</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E54" s="1" t="s">
-        <v>392</v>
+        <v>477</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>393</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E55" s="1" t="s">
-        <v>394</v>
+        <v>479</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>395</v>
+        <v>480</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="1" t="s">
-        <v>396</v>
+        <v>481</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>397</v>
+        <v>482</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="1" t="s">
-        <v>398</v>
+        <v>483</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>399</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E58" s="1" t="s">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>401</v>
+        <v>486</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E59" s="1" t="s">
-        <v>402</v>
+        <v>487</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>403</v>
+        <v>488</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E60" s="1" t="s">
-        <v>404</v>
+        <v>489</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>405</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E61" s="1" t="s">
-        <v>406</v>
+        <v>491</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>407</v>
+        <v>492</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E62" s="1" t="s">
-        <v>408</v>
+        <v>493</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>409</v>
+        <v>494</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E63" s="1" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>411</v>
+        <v>496</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E64" s="1" t="s">
-        <v>412</v>
+        <v>497</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>413</v>
+        <v>498</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E65" s="1" t="s">
-        <v>414</v>
+        <v>499</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>415</v>
+        <v>500</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E66" s="1" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>416</v>
+        <v>501</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L67" s="1" t="s">
-        <v>417</v>
+        <v>502</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L68" s="1" t="s">
-        <v>418</v>
+        <v>503</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L69" s="1" t="s">
-        <v>419</v>
+        <v>504</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L70" s="1" t="s">
-        <v>420</v>
+        <v>505</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L71" s="1" t="s">
-        <v>421</v>
+        <v>506</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L72" s="1" t="s">
-        <v>422</v>
+        <v>507</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L73" s="1" t="s">
-        <v>423</v>
+        <v>508</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L74" s="1" t="s">
-        <v>424</v>
+        <v>509</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L75" s="1" t="s">
-        <v>425</v>
+        <v>510</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L76" s="1" t="s">
-        <v>426</v>
+        <v>511</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L77" s="1" t="s">
-        <v>427</v>
+        <v>512</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L78" s="1" t="s">
-        <v>428</v>
+        <v>513</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L79" s="1" t="s">
-        <v>429</v>
+        <v>514</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L80" s="1" t="s">
-        <v>430</v>
+        <v>515</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L81" s="1" t="s">
-        <v>431</v>
+        <v>516</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L82" s="1" t="s">
-        <v>432</v>
+        <v>517</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L83" s="1" t="s">
-        <v>433</v>
+        <v>518</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L84" s="1" t="s">
-        <v>434</v>
+        <v>519</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L85" s="1" t="s">
-        <v>435</v>
+        <v>520</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L86" s="1" t="s">
-        <v>436</v>
+        <v>521</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L87" s="1" t="s">
-        <v>437</v>
+        <v>522</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L88" s="1" t="s">
-        <v>438</v>
+        <v>523</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L89" s="1" t="s">
-        <v>439</v>
+        <v>524</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L90" s="1" t="s">
-        <v>440</v>
+        <v>525</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L91" s="1" t="s">
-        <v>441</v>
+        <v>526</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L92" s="1" t="s">
-        <v>442</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L93" s="1" t="s">
-        <v>443</v>
+        <v>528</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L94" s="1" t="s">
-        <v>444</v>
+        <v>529</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L95" s="1" t="s">
-        <v>445</v>
+        <v>530</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L96" s="1" t="s">
-        <v>446</v>
+        <v>531</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L97" s="1" t="s">
-        <v>447</v>
+        <v>532</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L98" s="1" t="s">
-        <v>448</v>
+        <v>533</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L99" s="1" t="s">
-        <v>449</v>
+        <v>534</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L100" s="1" t="s">
-        <v>450</v>
+        <v>535</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L101" s="1" t="s">
-        <v>451</v>
+        <v>536</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L102" s="1" t="s">
-        <v>452</v>
+        <v>537</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L103" s="1" t="s">
-        <v>453</v>
+        <v>538</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L104" s="1" t="s">
-        <v>454</v>
+        <v>539</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L105" s="1" t="s">
-        <v>455</v>
+        <v>540</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L106" s="1" t="s">
-        <v>456</v>
+        <v>541</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L107" s="1" t="s">
-        <v>457</v>
+        <v>542</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L108" s="1" t="s">
-        <v>458</v>
+        <v>543</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L109" s="1" t="s">
-        <v>459</v>
+        <v>544</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L110" s="1" t="s">
-        <v>460</v>
+        <v>545</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L111" s="1" t="s">
-        <v>461</v>
+        <v>546</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L112" s="1" t="s">
-        <v>462</v>
+        <v>547</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L113" s="1" t="s">
-        <v>463</v>
+        <v>548</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L114" s="1" t="s">
-        <v>464</v>
+        <v>549</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L115" s="1" t="s">
-        <v>465</v>
+        <v>550</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L116" s="1" t="s">
-        <v>466</v>
+        <v>551</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L117" s="1" t="s">
-        <v>467</v>
+        <v>552</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L118" s="1" t="s">
-        <v>468</v>
+        <v>553</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L119" s="1" t="s">
-        <v>469</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L120" s="1" t="s">
-        <v>470</v>
+        <v>555</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L121" s="1" t="s">
-        <v>471</v>
+        <v>556</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L122" s="1" t="s">
-        <v>472</v>
+        <v>557</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L123" s="1" t="s">
-        <v>473</v>
+        <v>558</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L124" s="1" t="s">
-        <v>474</v>
+        <v>559</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L125" s="1" t="s">
-        <v>475</v>
+        <v>560</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L126" s="1" t="s">
-        <v>476</v>
+        <v>561</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L127" s="1" t="s">
-        <v>477</v>
+        <v>562</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L128" s="1" t="s">
-        <v>478</v>
+        <v>563</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L129" s="1" t="s">
-        <v>479</v>
+        <v>564</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L130" s="1" t="s">
-        <v>480</v>
+        <v>565</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L131" s="1" t="s">
-        <v>481</v>
+        <v>566</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L132" s="1" t="s">
-        <v>482</v>
+        <v>567</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L133" s="1" t="s">
-        <v>483</v>
+        <v>568</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L134" s="1" t="s">
-        <v>484</v>
+        <v>569</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L135" s="1" t="s">
-        <v>485</v>
+        <v>570</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L136" s="1" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L137" s="1" t="s">
-        <v>487</v>
+        <v>572</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L138" s="1" t="s">
-        <v>488</v>
+        <v>573</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L139" s="1" t="s">
-        <v>489</v>
+        <v>574</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L140" s="1" t="s">
-        <v>490</v>
+        <v>575</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L141" s="1" t="s">
-        <v>491</v>
+        <v>576</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L142" s="1" t="s">
-        <v>492</v>
+        <v>577</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L143" s="1" t="s">
-        <v>493</v>
+        <v>578</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L144" s="1" t="s">
-        <v>494</v>
+        <v>579</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L145" s="1" t="s">
-        <v>495</v>
+        <v>580</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L146" s="1" t="s">
-        <v>496</v>
+        <v>581</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L147" s="1" t="s">
-        <v>497</v>
+        <v>582</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L148" s="1" t="s">
-        <v>498</v>
+        <v>583</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L149" s="1" t="s">
-        <v>499</v>
+        <v>584</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L150" s="1" t="s">
-        <v>500</v>
+        <v>585</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L151" s="1" t="s">
-        <v>501</v>
+        <v>586</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L152" s="1" t="s">
-        <v>502</v>
+        <v>587</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L153" s="1" t="s">
-        <v>503</v>
+        <v>588</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L154" s="1" t="s">
-        <v>504</v>
+        <v>589</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L155" s="1" t="s">
-        <v>505</v>
+        <v>590</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L156" s="1" t="s">
-        <v>506</v>
+        <v>591</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L157" s="1" t="s">
-        <v>507</v>
+        <v>592</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L158" s="1" t="s">
-        <v>508</v>
+        <v>593</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L159" s="1" t="s">
-        <v>509</v>
+        <v>594</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L160" s="1" t="s">
-        <v>510</v>
+        <v>595</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L161" s="1" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L162" s="1" t="s">
-        <v>512</v>
+        <v>597</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L163" s="1" t="s">
-        <v>513</v>
+        <v>598</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L164" s="1" t="s">
-        <v>514</v>
+        <v>599</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L165" s="1" t="s">
-        <v>515</v>
+        <v>600</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L166" s="1" t="s">
-        <v>516</v>
+        <v>601</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L167" s="1" t="s">
-        <v>517</v>
+        <v>602</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L168" s="1" t="s">
-        <v>518</v>
+        <v>603</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L169" s="1" t="s">
-        <v>519</v>
+        <v>604</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L170" s="1" t="s">
-        <v>520</v>
+        <v>605</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L171" s="1" t="s">
-        <v>521</v>
+        <v>606</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L172" s="1" t="s">
-        <v>522</v>
+        <v>607</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L173" s="1" t="s">
-        <v>523</v>
+        <v>608</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L174" s="1" t="s">
-        <v>524</v>
+        <v>609</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L175" s="1" t="s">
-        <v>525</v>
+        <v>610</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L176" s="1" t="s">
-        <v>526</v>
+        <v>611</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L177" s="1" t="s">
-        <v>527</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
